--- a/templates/Nucleus Content.xlsx
+++ b/templates/Nucleus Content.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E309"/>
+  <dimension ref="A1:E297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B246" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C246" s="6" t="inlineStr"/>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="B247" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C247" s="6" t="inlineStr"/>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B248" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C248" s="6" t="inlineStr"/>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="B249" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C249" s="6" t="inlineStr"/>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="B250" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C250" s="6" t="inlineStr"/>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="B251" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C251" s="6" t="inlineStr"/>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B252" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C252" s="6" t="inlineStr"/>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="B253" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C253" s="6" t="inlineStr"/>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="B254" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C254" s="6" t="inlineStr"/>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="B255" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C255" s="6" t="inlineStr"/>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B256" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C256" s="6" t="inlineStr"/>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="B257" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C257" s="6" t="inlineStr"/>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="B258" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C258" s="6" t="inlineStr"/>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="B259" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C259" s="6" t="inlineStr"/>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B260" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C260" s="6" t="inlineStr"/>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="B261" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C261" s="6" t="inlineStr"/>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="B262" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C262" s="6" t="inlineStr"/>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="B263" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C263" s="6" t="inlineStr"/>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B264" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C264" s="6" t="inlineStr"/>
@@ -4721,7 +4721,7 @@
       </c>
       <c r="B265" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C265" s="6" t="inlineStr"/>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="B266" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C266" s="6" t="inlineStr"/>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="B267" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C267" s="6" t="inlineStr"/>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B268" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C268" s="6" t="inlineStr"/>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="B269" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C269" s="6" t="inlineStr"/>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="B270" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C270" s="6" t="inlineStr"/>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="B271" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C271" s="6" t="inlineStr"/>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B272" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C272" s="6" t="inlineStr"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="B273" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C273" s="6" t="inlineStr"/>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="B274" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C274" s="6" t="inlineStr"/>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="B275" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C275" s="6" t="inlineStr"/>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="B276" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C276" s="6" t="inlineStr"/>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="B277" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C277" s="6" t="inlineStr"/>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="B278" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C278" s="6" t="inlineStr"/>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="B279" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C279" s="6" t="inlineStr"/>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="B280" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C280" s="6" t="inlineStr"/>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="B281" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C281" s="6" t="inlineStr"/>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="B282" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C282" s="6" t="inlineStr"/>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="B283" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C283" s="6" t="inlineStr"/>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="B284" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C284" s="6" t="inlineStr"/>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="B285" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C285" s="6" t="inlineStr"/>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="B286" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C286" s="6" t="inlineStr"/>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="B287" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C287" s="6" t="inlineStr"/>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="B288" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C288" s="6" t="inlineStr"/>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="B289" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C289" s="6" t="inlineStr"/>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="B290" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C290" s="6" t="inlineStr"/>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="B291" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C291" s="6" t="inlineStr"/>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="B292" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C292" s="6" t="inlineStr"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="B293" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C293" s="6" t="inlineStr"/>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="B294" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C294" s="6" t="inlineStr"/>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="B295" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C295" s="6" t="inlineStr"/>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="B296" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C296" s="6" t="inlineStr"/>
@@ -5201,192 +5201,12 @@
       </c>
       <c r="B297" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C297" s="6" t="inlineStr"/>
       <c r="D297" s="6" t="inlineStr"/>
       <c r="E297" s="6" t="inlineStr"/>
-    </row>
-    <row r="298" ht="50" customHeight="1">
-      <c r="A298" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B298" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C298" s="6" t="inlineStr"/>
-      <c r="D298" s="6" t="inlineStr"/>
-      <c r="E298" s="6" t="inlineStr"/>
-    </row>
-    <row r="299" ht="50" customHeight="1">
-      <c r="A299" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B299" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C299" s="6" t="inlineStr"/>
-      <c r="D299" s="6" t="inlineStr"/>
-      <c r="E299" s="6" t="inlineStr"/>
-    </row>
-    <row r="300" ht="50" customHeight="1">
-      <c r="A300" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B300" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C300" s="6" t="inlineStr"/>
-      <c r="D300" s="6" t="inlineStr"/>
-      <c r="E300" s="6" t="inlineStr"/>
-    </row>
-    <row r="301" ht="50" customHeight="1">
-      <c r="A301" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B301" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C301" s="6" t="inlineStr"/>
-      <c r="D301" s="6" t="inlineStr"/>
-      <c r="E301" s="6" t="inlineStr"/>
-    </row>
-    <row r="302" ht="50" customHeight="1">
-      <c r="A302" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B302" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C302" s="6" t="inlineStr"/>
-      <c r="D302" s="6" t="inlineStr"/>
-      <c r="E302" s="6" t="inlineStr"/>
-    </row>
-    <row r="303" ht="50" customHeight="1">
-      <c r="A303" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B303" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C303" s="6" t="inlineStr"/>
-      <c r="D303" s="6" t="inlineStr"/>
-      <c r="E303" s="6" t="inlineStr"/>
-    </row>
-    <row r="304" ht="50" customHeight="1">
-      <c r="A304" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B304" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C304" s="6" t="inlineStr"/>
-      <c r="D304" s="6" t="inlineStr"/>
-      <c r="E304" s="6" t="inlineStr"/>
-    </row>
-    <row r="305" ht="50" customHeight="1">
-      <c r="A305" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B305" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C305" s="6" t="inlineStr"/>
-      <c r="D305" s="6" t="inlineStr"/>
-      <c r="E305" s="6" t="inlineStr"/>
-    </row>
-    <row r="306" ht="50" customHeight="1">
-      <c r="A306" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B306" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C306" s="6" t="inlineStr"/>
-      <c r="D306" s="6" t="inlineStr"/>
-      <c r="E306" s="6" t="inlineStr"/>
-    </row>
-    <row r="307" ht="50" customHeight="1">
-      <c r="A307" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B307" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C307" s="6" t="inlineStr"/>
-      <c r="D307" s="6" t="inlineStr"/>
-      <c r="E307" s="6" t="inlineStr"/>
-    </row>
-    <row r="308" ht="50" customHeight="1">
-      <c r="A308" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B308" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C308" s="6" t="inlineStr"/>
-      <c r="D308" s="6" t="inlineStr"/>
-      <c r="E308" s="6" t="inlineStr"/>
-    </row>
-    <row r="309" ht="50" customHeight="1">
-      <c r="A309" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B309" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C309" s="6" t="inlineStr"/>
-      <c r="D309" s="6" t="inlineStr"/>
-      <c r="E309" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5399,7 +5219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F617"/>
+  <dimension ref="A1:F593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13590,7 +13410,7 @@
       </c>
       <c r="B490" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C490" s="6" t="inlineStr"/>
@@ -13606,7 +13426,7 @@
       </c>
       <c r="B491" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C491" s="6" t="inlineStr"/>
@@ -13622,7 +13442,7 @@
       </c>
       <c r="B492" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C492" s="6" t="inlineStr"/>
@@ -13638,7 +13458,7 @@
       </c>
       <c r="B493" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C493" s="6" t="inlineStr"/>
@@ -13654,7 +13474,7 @@
       </c>
       <c r="B494" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C494" s="6" t="inlineStr"/>
@@ -13670,7 +13490,7 @@
       </c>
       <c r="B495" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C495" s="6" t="inlineStr"/>
@@ -13686,7 +13506,7 @@
       </c>
       <c r="B496" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C496" s="6" t="inlineStr"/>
@@ -13702,7 +13522,7 @@
       </c>
       <c r="B497" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C497" s="6" t="inlineStr"/>
@@ -13718,7 +13538,7 @@
       </c>
       <c r="B498" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C498" s="6" t="inlineStr"/>
@@ -13734,7 +13554,7 @@
       </c>
       <c r="B499" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C499" s="6" t="inlineStr"/>
@@ -13750,7 +13570,7 @@
       </c>
       <c r="B500" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C500" s="6" t="inlineStr"/>
@@ -13766,7 +13586,7 @@
       </c>
       <c r="B501" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C501" s="6" t="inlineStr"/>
@@ -13782,7 +13602,7 @@
       </c>
       <c r="B502" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C502" s="6" t="inlineStr"/>
@@ -13798,7 +13618,7 @@
       </c>
       <c r="B503" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C503" s="6" t="inlineStr"/>
@@ -13814,7 +13634,7 @@
       </c>
       <c r="B504" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C504" s="6" t="inlineStr"/>
@@ -13830,7 +13650,7 @@
       </c>
       <c r="B505" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C505" s="6" t="inlineStr"/>
@@ -13846,7 +13666,7 @@
       </c>
       <c r="B506" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C506" s="6" t="inlineStr"/>
@@ -13862,7 +13682,7 @@
       </c>
       <c r="B507" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C507" s="6" t="inlineStr"/>
@@ -13878,7 +13698,7 @@
       </c>
       <c r="B508" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C508" s="6" t="inlineStr"/>
@@ -13894,7 +13714,7 @@
       </c>
       <c r="B509" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C509" s="6" t="inlineStr"/>
@@ -13910,7 +13730,7 @@
       </c>
       <c r="B510" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C510" s="6" t="inlineStr"/>
@@ -13926,7 +13746,7 @@
       </c>
       <c r="B511" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C511" s="6" t="inlineStr"/>
@@ -13942,7 +13762,7 @@
       </c>
       <c r="B512" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C512" s="6" t="inlineStr"/>
@@ -13958,7 +13778,7 @@
       </c>
       <c r="B513" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C513" s="6" t="inlineStr"/>
@@ -13974,7 +13794,7 @@
       </c>
       <c r="B514" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C514" s="6" t="inlineStr"/>
@@ -13990,7 +13810,7 @@
       </c>
       <c r="B515" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C515" s="6" t="inlineStr"/>
@@ -14006,7 +13826,7 @@
       </c>
       <c r="B516" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C516" s="6" t="inlineStr"/>
@@ -14022,7 +13842,7 @@
       </c>
       <c r="B517" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C517" s="6" t="inlineStr"/>
@@ -14038,7 +13858,7 @@
       </c>
       <c r="B518" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C518" s="6" t="inlineStr"/>
@@ -14054,7 +13874,7 @@
       </c>
       <c r="B519" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C519" s="6" t="inlineStr"/>
@@ -14070,7 +13890,7 @@
       </c>
       <c r="B520" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C520" s="6" t="inlineStr"/>
@@ -14086,7 +13906,7 @@
       </c>
       <c r="B521" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C521" s="6" t="inlineStr"/>
@@ -14102,7 +13922,7 @@
       </c>
       <c r="B522" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C522" s="6" t="inlineStr"/>
@@ -14118,7 +13938,7 @@
       </c>
       <c r="B523" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C523" s="6" t="inlineStr"/>
@@ -14134,7 +13954,7 @@
       </c>
       <c r="B524" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C524" s="6" t="inlineStr"/>
@@ -14150,7 +13970,7 @@
       </c>
       <c r="B525" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C525" s="6" t="inlineStr"/>
@@ -14166,7 +13986,7 @@
       </c>
       <c r="B526" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C526" s="6" t="inlineStr"/>
@@ -14182,7 +14002,7 @@
       </c>
       <c r="B527" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C527" s="6" t="inlineStr"/>
@@ -14198,7 +14018,7 @@
       </c>
       <c r="B528" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C528" s="6" t="inlineStr"/>
@@ -14214,7 +14034,7 @@
       </c>
       <c r="B529" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C529" s="6" t="inlineStr"/>
@@ -14230,7 +14050,7 @@
       </c>
       <c r="B530" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C530" s="6" t="inlineStr"/>
@@ -14246,7 +14066,7 @@
       </c>
       <c r="B531" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C531" s="6" t="inlineStr"/>
@@ -14262,7 +14082,7 @@
       </c>
       <c r="B532" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C532" s="6" t="inlineStr"/>
@@ -14278,7 +14098,7 @@
       </c>
       <c r="B533" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C533" s="6" t="inlineStr"/>
@@ -14294,7 +14114,7 @@
       </c>
       <c r="B534" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C534" s="6" t="inlineStr"/>
@@ -14310,7 +14130,7 @@
       </c>
       <c r="B535" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C535" s="6" t="inlineStr"/>
@@ -14326,7 +14146,7 @@
       </c>
       <c r="B536" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C536" s="6" t="inlineStr"/>
@@ -14342,7 +14162,7 @@
       </c>
       <c r="B537" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C537" s="6" t="inlineStr"/>
@@ -14358,7 +14178,7 @@
       </c>
       <c r="B538" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C538" s="6" t="inlineStr"/>
@@ -14374,7 +14194,7 @@
       </c>
       <c r="B539" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C539" s="6" t="inlineStr"/>
@@ -14390,7 +14210,7 @@
       </c>
       <c r="B540" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C540" s="6" t="inlineStr"/>
@@ -14406,7 +14226,7 @@
       </c>
       <c r="B541" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C541" s="6" t="inlineStr"/>
@@ -14422,7 +14242,7 @@
       </c>
       <c r="B542" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C542" s="6" t="inlineStr"/>
@@ -14438,7 +14258,7 @@
       </c>
       <c r="B543" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C543" s="6" t="inlineStr"/>
@@ -14454,7 +14274,7 @@
       </c>
       <c r="B544" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C544" s="6" t="inlineStr"/>
@@ -14470,7 +14290,7 @@
       </c>
       <c r="B545" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C545" s="6" t="inlineStr"/>
@@ -14486,7 +14306,7 @@
       </c>
       <c r="B546" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C546" s="6" t="inlineStr"/>
@@ -14502,7 +14322,7 @@
       </c>
       <c r="B547" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C547" s="6" t="inlineStr"/>
@@ -14518,7 +14338,7 @@
       </c>
       <c r="B548" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C548" s="6" t="inlineStr"/>
@@ -14534,7 +14354,7 @@
       </c>
       <c r="B549" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C549" s="6" t="inlineStr"/>
@@ -14550,7 +14370,7 @@
       </c>
       <c r="B550" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C550" s="6" t="inlineStr"/>
@@ -14566,7 +14386,7 @@
       </c>
       <c r="B551" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C551" s="6" t="inlineStr"/>
@@ -14582,7 +14402,7 @@
       </c>
       <c r="B552" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C552" s="6" t="inlineStr"/>
@@ -14598,7 +14418,7 @@
       </c>
       <c r="B553" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C553" s="6" t="inlineStr"/>
@@ -14614,7 +14434,7 @@
       </c>
       <c r="B554" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C554" s="6" t="inlineStr"/>
@@ -14630,7 +14450,7 @@
       </c>
       <c r="B555" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C555" s="6" t="inlineStr"/>
@@ -14646,7 +14466,7 @@
       </c>
       <c r="B556" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C556" s="6" t="inlineStr"/>
@@ -14662,7 +14482,7 @@
       </c>
       <c r="B557" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C557" s="6" t="inlineStr"/>
@@ -14678,7 +14498,7 @@
       </c>
       <c r="B558" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C558" s="6" t="inlineStr"/>
@@ -14694,7 +14514,7 @@
       </c>
       <c r="B559" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C559" s="6" t="inlineStr"/>
@@ -14710,7 +14530,7 @@
       </c>
       <c r="B560" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C560" s="6" t="inlineStr"/>
@@ -14726,7 +14546,7 @@
       </c>
       <c r="B561" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C561" s="6" t="inlineStr"/>
@@ -14742,7 +14562,7 @@
       </c>
       <c r="B562" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C562" s="6" t="inlineStr"/>
@@ -14758,7 +14578,7 @@
       </c>
       <c r="B563" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C563" s="6" t="inlineStr"/>
@@ -14774,7 +14594,7 @@
       </c>
       <c r="B564" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C564" s="6" t="inlineStr"/>
@@ -14790,7 +14610,7 @@
       </c>
       <c r="B565" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C565" s="6" t="inlineStr"/>
@@ -14806,7 +14626,7 @@
       </c>
       <c r="B566" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C566" s="6" t="inlineStr"/>
@@ -14822,7 +14642,7 @@
       </c>
       <c r="B567" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C567" s="6" t="inlineStr"/>
@@ -14838,7 +14658,7 @@
       </c>
       <c r="B568" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C568" s="6" t="inlineStr"/>
@@ -14854,7 +14674,7 @@
       </c>
       <c r="B569" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C569" s="6" t="inlineStr"/>
@@ -14870,7 +14690,7 @@
       </c>
       <c r="B570" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C570" s="6" t="inlineStr"/>
@@ -14886,7 +14706,7 @@
       </c>
       <c r="B571" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C571" s="6" t="inlineStr"/>
@@ -14902,7 +14722,7 @@
       </c>
       <c r="B572" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C572" s="6" t="inlineStr"/>
@@ -14918,7 +14738,7 @@
       </c>
       <c r="B573" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C573" s="6" t="inlineStr"/>
@@ -14934,7 +14754,7 @@
       </c>
       <c r="B574" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C574" s="6" t="inlineStr"/>
@@ -14950,7 +14770,7 @@
       </c>
       <c r="B575" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C575" s="6" t="inlineStr"/>
@@ -14966,7 +14786,7 @@
       </c>
       <c r="B576" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C576" s="6" t="inlineStr"/>
@@ -14982,7 +14802,7 @@
       </c>
       <c r="B577" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C577" s="6" t="inlineStr"/>
@@ -14998,7 +14818,7 @@
       </c>
       <c r="B578" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C578" s="6" t="inlineStr"/>
@@ -15014,7 +14834,7 @@
       </c>
       <c r="B579" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C579" s="6" t="inlineStr"/>
@@ -15030,7 +14850,7 @@
       </c>
       <c r="B580" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C580" s="6" t="inlineStr"/>
@@ -15046,7 +14866,7 @@
       </c>
       <c r="B581" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C581" s="6" t="inlineStr"/>
@@ -15062,7 +14882,7 @@
       </c>
       <c r="B582" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C582" s="6" t="inlineStr"/>
@@ -15078,7 +14898,7 @@
       </c>
       <c r="B583" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C583" s="6" t="inlineStr"/>
@@ -15094,7 +14914,7 @@
       </c>
       <c r="B584" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C584" s="6" t="inlineStr"/>
@@ -15110,7 +14930,7 @@
       </c>
       <c r="B585" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C585" s="6" t="inlineStr"/>
@@ -15126,7 +14946,7 @@
       </c>
       <c r="B586" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C586" s="6" t="inlineStr"/>
@@ -15142,7 +14962,7 @@
       </c>
       <c r="B587" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C587" s="6" t="inlineStr"/>
@@ -15158,7 +14978,7 @@
       </c>
       <c r="B588" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C588" s="6" t="inlineStr"/>
@@ -15174,7 +14994,7 @@
       </c>
       <c r="B589" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C589" s="6" t="inlineStr"/>
@@ -15190,7 +15010,7 @@
       </c>
       <c r="B590" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C590" s="6" t="inlineStr"/>
@@ -15206,7 +15026,7 @@
       </c>
       <c r="B591" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C591" s="6" t="inlineStr"/>
@@ -15222,7 +15042,7 @@
       </c>
       <c r="B592" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C592" s="6" t="inlineStr"/>
@@ -15238,397 +15058,13 @@
       </c>
       <c r="B593" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C593" s="6" t="inlineStr"/>
       <c r="D593" s="6" t="inlineStr"/>
       <c r="E593" s="6" t="inlineStr"/>
       <c r="F593" s="6" t="inlineStr"/>
-    </row>
-    <row r="594" ht="40" customHeight="1">
-      <c r="A594" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B594" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C594" s="6" t="inlineStr"/>
-      <c r="D594" s="6" t="inlineStr"/>
-      <c r="E594" s="6" t="inlineStr"/>
-      <c r="F594" s="6" t="inlineStr"/>
-    </row>
-    <row r="595" ht="40" customHeight="1">
-      <c r="A595" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B595" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C595" s="6" t="inlineStr"/>
-      <c r="D595" s="6" t="inlineStr"/>
-      <c r="E595" s="6" t="inlineStr"/>
-      <c r="F595" s="6" t="inlineStr"/>
-    </row>
-    <row r="596" ht="40" customHeight="1">
-      <c r="A596" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B596" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C596" s="6" t="inlineStr"/>
-      <c r="D596" s="6" t="inlineStr"/>
-      <c r="E596" s="6" t="inlineStr"/>
-      <c r="F596" s="6" t="inlineStr"/>
-    </row>
-    <row r="597" ht="40" customHeight="1">
-      <c r="A597" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B597" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C597" s="6" t="inlineStr"/>
-      <c r="D597" s="6" t="inlineStr"/>
-      <c r="E597" s="6" t="inlineStr"/>
-      <c r="F597" s="6" t="inlineStr"/>
-    </row>
-    <row r="598" ht="40" customHeight="1">
-      <c r="A598" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B598" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C598" s="6" t="inlineStr"/>
-      <c r="D598" s="6" t="inlineStr"/>
-      <c r="E598" s="6" t="inlineStr"/>
-      <c r="F598" s="6" t="inlineStr"/>
-    </row>
-    <row r="599" ht="40" customHeight="1">
-      <c r="A599" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B599" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C599" s="6" t="inlineStr"/>
-      <c r="D599" s="6" t="inlineStr"/>
-      <c r="E599" s="6" t="inlineStr"/>
-      <c r="F599" s="6" t="inlineStr"/>
-    </row>
-    <row r="600" ht="40" customHeight="1">
-      <c r="A600" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B600" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C600" s="6" t="inlineStr"/>
-      <c r="D600" s="6" t="inlineStr"/>
-      <c r="E600" s="6" t="inlineStr"/>
-      <c r="F600" s="6" t="inlineStr"/>
-    </row>
-    <row r="601" ht="40" customHeight="1">
-      <c r="A601" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B601" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C601" s="6" t="inlineStr"/>
-      <c r="D601" s="6" t="inlineStr"/>
-      <c r="E601" s="6" t="inlineStr"/>
-      <c r="F601" s="6" t="inlineStr"/>
-    </row>
-    <row r="602" ht="40" customHeight="1">
-      <c r="A602" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B602" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C602" s="6" t="inlineStr"/>
-      <c r="D602" s="6" t="inlineStr"/>
-      <c r="E602" s="6" t="inlineStr"/>
-      <c r="F602" s="6" t="inlineStr"/>
-    </row>
-    <row r="603" ht="40" customHeight="1">
-      <c r="A603" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B603" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C603" s="6" t="inlineStr"/>
-      <c r="D603" s="6" t="inlineStr"/>
-      <c r="E603" s="6" t="inlineStr"/>
-      <c r="F603" s="6" t="inlineStr"/>
-    </row>
-    <row r="604" ht="40" customHeight="1">
-      <c r="A604" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B604" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C604" s="6" t="inlineStr"/>
-      <c r="D604" s="6" t="inlineStr"/>
-      <c r="E604" s="6" t="inlineStr"/>
-      <c r="F604" s="6" t="inlineStr"/>
-    </row>
-    <row r="605" ht="40" customHeight="1">
-      <c r="A605" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B605" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C605" s="6" t="inlineStr"/>
-      <c r="D605" s="6" t="inlineStr"/>
-      <c r="E605" s="6" t="inlineStr"/>
-      <c r="F605" s="6" t="inlineStr"/>
-    </row>
-    <row r="606" ht="40" customHeight="1">
-      <c r="A606" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B606" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C606" s="6" t="inlineStr"/>
-      <c r="D606" s="6" t="inlineStr"/>
-      <c r="E606" s="6" t="inlineStr"/>
-      <c r="F606" s="6" t="inlineStr"/>
-    </row>
-    <row r="607" ht="40" customHeight="1">
-      <c r="A607" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B607" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C607" s="6" t="inlineStr"/>
-      <c r="D607" s="6" t="inlineStr"/>
-      <c r="E607" s="6" t="inlineStr"/>
-      <c r="F607" s="6" t="inlineStr"/>
-    </row>
-    <row r="608" ht="40" customHeight="1">
-      <c r="A608" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B608" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C608" s="6" t="inlineStr"/>
-      <c r="D608" s="6" t="inlineStr"/>
-      <c r="E608" s="6" t="inlineStr"/>
-      <c r="F608" s="6" t="inlineStr"/>
-    </row>
-    <row r="609" ht="40" customHeight="1">
-      <c r="A609" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B609" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C609" s="6" t="inlineStr"/>
-      <c r="D609" s="6" t="inlineStr"/>
-      <c r="E609" s="6" t="inlineStr"/>
-      <c r="F609" s="6" t="inlineStr"/>
-    </row>
-    <row r="610" ht="40" customHeight="1">
-      <c r="A610" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B610" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C610" s="6" t="inlineStr"/>
-      <c r="D610" s="6" t="inlineStr"/>
-      <c r="E610" s="6" t="inlineStr"/>
-      <c r="F610" s="6" t="inlineStr"/>
-    </row>
-    <row r="611" ht="40" customHeight="1">
-      <c r="A611" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B611" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C611" s="6" t="inlineStr"/>
-      <c r="D611" s="6" t="inlineStr"/>
-      <c r="E611" s="6" t="inlineStr"/>
-      <c r="F611" s="6" t="inlineStr"/>
-    </row>
-    <row r="612" ht="40" customHeight="1">
-      <c r="A612" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B612" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C612" s="6" t="inlineStr"/>
-      <c r="D612" s="6" t="inlineStr"/>
-      <c r="E612" s="6" t="inlineStr"/>
-      <c r="F612" s="6" t="inlineStr"/>
-    </row>
-    <row r="613" ht="40" customHeight="1">
-      <c r="A613" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B613" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C613" s="6" t="inlineStr"/>
-      <c r="D613" s="6" t="inlineStr"/>
-      <c r="E613" s="6" t="inlineStr"/>
-      <c r="F613" s="6" t="inlineStr"/>
-    </row>
-    <row r="614" ht="40" customHeight="1">
-      <c r="A614" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B614" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C614" s="6" t="inlineStr"/>
-      <c r="D614" s="6" t="inlineStr"/>
-      <c r="E614" s="6" t="inlineStr"/>
-      <c r="F614" s="6" t="inlineStr"/>
-    </row>
-    <row r="615" ht="40" customHeight="1">
-      <c r="A615" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B615" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C615" s="6" t="inlineStr"/>
-      <c r="D615" s="6" t="inlineStr"/>
-      <c r="E615" s="6" t="inlineStr"/>
-      <c r="F615" s="6" t="inlineStr"/>
-    </row>
-    <row r="616" ht="40" customHeight="1">
-      <c r="A616" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B616" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C616" s="6" t="inlineStr"/>
-      <c r="D616" s="6" t="inlineStr"/>
-      <c r="E616" s="6" t="inlineStr"/>
-      <c r="F616" s="6" t="inlineStr"/>
-    </row>
-    <row r="617" ht="40" customHeight="1">
-      <c r="A617" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B617" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C617" s="6" t="inlineStr"/>
-      <c r="D617" s="6" t="inlineStr"/>
-      <c r="E617" s="6" t="inlineStr"/>
-      <c r="F617" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15641,7 +15077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1541"/>
+  <dimension ref="A1:J1481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -46676,7 +46112,7 @@
       </c>
       <c r="B1222" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C1222" s="13" t="inlineStr">
@@ -46700,7 +46136,7 @@
       </c>
       <c r="B1223" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C1223" s="13" t="inlineStr">
@@ -46724,7 +46160,7 @@
       </c>
       <c r="B1224" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C1224" s="13" t="inlineStr">
@@ -46748,7 +46184,7 @@
       </c>
       <c r="B1225" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C1225" s="13" t="inlineStr">
@@ -46772,7 +46208,7 @@
       </c>
       <c r="B1226" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C1226" s="13" t="inlineStr">
@@ -46796,7 +46232,7 @@
       </c>
       <c r="B1227" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C1227" s="13" t="inlineStr">
@@ -46820,7 +46256,7 @@
       </c>
       <c r="B1228" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C1228" s="13" t="inlineStr">
@@ -46844,7 +46280,7 @@
       </c>
       <c r="B1229" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C1229" s="13" t="inlineStr">
@@ -46868,7 +46304,7 @@
       </c>
       <c r="B1230" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C1230" s="13" t="inlineStr">
@@ -46892,7 +46328,7 @@
       </c>
       <c r="B1231" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C1231" s="13" t="inlineStr">
@@ -46916,7 +46352,7 @@
       </c>
       <c r="B1232" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C1232" s="13" t="inlineStr">
@@ -46940,7 +46376,7 @@
       </c>
       <c r="B1233" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C1233" s="13" t="inlineStr">
@@ -46964,7 +46400,7 @@
       </c>
       <c r="B1234" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C1234" s="13" t="inlineStr">
@@ -46988,7 +46424,7 @@
       </c>
       <c r="B1235" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C1235" s="13" t="inlineStr">
@@ -47012,7 +46448,7 @@
       </c>
       <c r="B1236" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C1236" s="13" t="inlineStr">
@@ -47036,7 +46472,7 @@
       </c>
       <c r="B1237" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C1237" s="13" t="inlineStr">
@@ -47060,7 +46496,7 @@
       </c>
       <c r="B1238" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C1238" s="13" t="inlineStr">
@@ -47084,7 +46520,7 @@
       </c>
       <c r="B1239" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C1239" s="13" t="inlineStr">
@@ -47108,7 +46544,7 @@
       </c>
       <c r="B1240" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C1240" s="13" t="inlineStr">
@@ -47132,7 +46568,7 @@
       </c>
       <c r="B1241" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C1241" s="13" t="inlineStr">
@@ -47156,7 +46592,7 @@
       </c>
       <c r="B1242" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C1242" s="13" t="inlineStr">
@@ -47180,7 +46616,7 @@
       </c>
       <c r="B1243" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C1243" s="13" t="inlineStr">
@@ -47204,7 +46640,7 @@
       </c>
       <c r="B1244" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C1244" s="13" t="inlineStr">
@@ -47228,7 +46664,7 @@
       </c>
       <c r="B1245" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C1245" s="13" t="inlineStr">
@@ -47252,7 +46688,7 @@
       </c>
       <c r="B1246" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C1246" s="13" t="inlineStr">
@@ -47276,7 +46712,7 @@
       </c>
       <c r="B1247" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C1247" s="13" t="inlineStr">
@@ -47300,7 +46736,7 @@
       </c>
       <c r="B1248" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C1248" s="13" t="inlineStr">
@@ -47324,7 +46760,7 @@
       </c>
       <c r="B1249" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C1249" s="13" t="inlineStr">
@@ -47348,7 +46784,7 @@
       </c>
       <c r="B1250" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C1250" s="13" t="inlineStr">
@@ -47372,7 +46808,7 @@
       </c>
       <c r="B1251" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C1251" s="13" t="inlineStr">
@@ -47396,7 +46832,7 @@
       </c>
       <c r="B1252" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C1252" s="13" t="inlineStr">
@@ -47420,7 +46856,7 @@
       </c>
       <c r="B1253" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C1253" s="13" t="inlineStr">
@@ -47444,7 +46880,7 @@
       </c>
       <c r="B1254" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C1254" s="13" t="inlineStr">
@@ -47468,7 +46904,7 @@
       </c>
       <c r="B1255" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C1255" s="13" t="inlineStr">
@@ -47492,7 +46928,7 @@
       </c>
       <c r="B1256" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C1256" s="13" t="inlineStr">
@@ -47516,7 +46952,7 @@
       </c>
       <c r="B1257" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C1257" s="13" t="inlineStr">
@@ -47540,7 +46976,7 @@
       </c>
       <c r="B1258" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C1258" s="13" t="inlineStr">
@@ -47564,7 +47000,7 @@
       </c>
       <c r="B1259" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C1259" s="13" t="inlineStr">
@@ -47588,7 +47024,7 @@
       </c>
       <c r="B1260" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C1260" s="13" t="inlineStr">
@@ -47612,7 +47048,7 @@
       </c>
       <c r="B1261" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C1261" s="13" t="inlineStr">
@@ -47636,7 +47072,7 @@
       </c>
       <c r="B1262" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C1262" s="13" t="inlineStr">
@@ -47660,7 +47096,7 @@
       </c>
       <c r="B1263" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C1263" s="13" t="inlineStr">
@@ -47684,7 +47120,7 @@
       </c>
       <c r="B1264" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C1264" s="13" t="inlineStr">
@@ -47708,7 +47144,7 @@
       </c>
       <c r="B1265" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C1265" s="13" t="inlineStr">
@@ -47732,7 +47168,7 @@
       </c>
       <c r="B1266" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C1266" s="13" t="inlineStr">
@@ -47756,7 +47192,7 @@
       </c>
       <c r="B1267" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C1267" s="13" t="inlineStr">
@@ -47780,7 +47216,7 @@
       </c>
       <c r="B1268" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C1268" s="13" t="inlineStr">
@@ -47804,7 +47240,7 @@
       </c>
       <c r="B1269" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C1269" s="13" t="inlineStr">
@@ -47828,7 +47264,7 @@
       </c>
       <c r="B1270" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C1270" s="13" t="inlineStr">
@@ -47852,7 +47288,7 @@
       </c>
       <c r="B1271" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C1271" s="13" t="inlineStr">
@@ -47876,7 +47312,7 @@
       </c>
       <c r="B1272" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C1272" s="13" t="inlineStr">
@@ -47900,7 +47336,7 @@
       </c>
       <c r="B1273" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C1273" s="13" t="inlineStr">
@@ -47924,7 +47360,7 @@
       </c>
       <c r="B1274" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C1274" s="13" t="inlineStr">
@@ -47948,7 +47384,7 @@
       </c>
       <c r="B1275" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C1275" s="13" t="inlineStr">
@@ -47972,7 +47408,7 @@
       </c>
       <c r="B1276" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C1276" s="13" t="inlineStr">
@@ -47996,7 +47432,7 @@
       </c>
       <c r="B1277" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C1277" s="13" t="inlineStr">
@@ -48020,7 +47456,7 @@
       </c>
       <c r="B1278" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C1278" s="13" t="inlineStr">
@@ -48044,7 +47480,7 @@
       </c>
       <c r="B1279" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C1279" s="13" t="inlineStr">
@@ -48068,7 +47504,7 @@
       </c>
       <c r="B1280" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C1280" s="13" t="inlineStr">
@@ -48092,7 +47528,7 @@
       </c>
       <c r="B1281" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C1281" s="13" t="inlineStr">
@@ -48116,7 +47552,7 @@
       </c>
       <c r="B1282" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C1282" s="13" t="inlineStr">
@@ -48140,7 +47576,7 @@
       </c>
       <c r="B1283" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C1283" s="13" t="inlineStr">
@@ -48164,7 +47600,7 @@
       </c>
       <c r="B1284" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C1284" s="13" t="inlineStr">
@@ -48188,7 +47624,7 @@
       </c>
       <c r="B1285" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C1285" s="13" t="inlineStr">
@@ -48212,7 +47648,7 @@
       </c>
       <c r="B1286" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C1286" s="13" t="inlineStr">
@@ -48236,7 +47672,7 @@
       </c>
       <c r="B1287" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C1287" s="13" t="inlineStr">
@@ -48260,7 +47696,7 @@
       </c>
       <c r="B1288" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C1288" s="13" t="inlineStr">
@@ -48284,7 +47720,7 @@
       </c>
       <c r="B1289" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C1289" s="13" t="inlineStr">
@@ -48308,7 +47744,7 @@
       </c>
       <c r="B1290" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C1290" s="13" t="inlineStr">
@@ -48332,7 +47768,7 @@
       </c>
       <c r="B1291" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C1291" s="13" t="inlineStr">
@@ -48356,7 +47792,7 @@
       </c>
       <c r="B1292" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C1292" s="13" t="inlineStr">
@@ -48380,7 +47816,7 @@
       </c>
       <c r="B1293" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C1293" s="13" t="inlineStr">
@@ -48404,7 +47840,7 @@
       </c>
       <c r="B1294" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C1294" s="13" t="inlineStr">
@@ -48428,7 +47864,7 @@
       </c>
       <c r="B1295" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C1295" s="13" t="inlineStr">
@@ -48452,7 +47888,7 @@
       </c>
       <c r="B1296" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C1296" s="13" t="inlineStr">
@@ -48476,7 +47912,7 @@
       </c>
       <c r="B1297" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C1297" s="13" t="inlineStr">
@@ -48500,7 +47936,7 @@
       </c>
       <c r="B1298" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C1298" s="13" t="inlineStr">
@@ -48524,7 +47960,7 @@
       </c>
       <c r="B1299" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C1299" s="13" t="inlineStr">
@@ -48548,7 +47984,7 @@
       </c>
       <c r="B1300" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C1300" s="13" t="inlineStr">
@@ -48572,7 +48008,7 @@
       </c>
       <c r="B1301" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C1301" s="13" t="inlineStr">
@@ -48596,7 +48032,7 @@
       </c>
       <c r="B1302" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C1302" s="13" t="inlineStr">
@@ -48620,7 +48056,7 @@
       </c>
       <c r="B1303" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C1303" s="13" t="inlineStr">
@@ -48644,7 +48080,7 @@
       </c>
       <c r="B1304" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C1304" s="13" t="inlineStr">
@@ -48668,7 +48104,7 @@
       </c>
       <c r="B1305" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C1305" s="13" t="inlineStr">
@@ -48692,7 +48128,7 @@
       </c>
       <c r="B1306" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C1306" s="13" t="inlineStr">
@@ -48716,7 +48152,7 @@
       </c>
       <c r="B1307" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C1307" s="13" t="inlineStr">
@@ -48740,7 +48176,7 @@
       </c>
       <c r="B1308" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C1308" s="13" t="inlineStr">
@@ -48764,7 +48200,7 @@
       </c>
       <c r="B1309" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C1309" s="13" t="inlineStr">
@@ -48788,7 +48224,7 @@
       </c>
       <c r="B1310" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C1310" s="13" t="inlineStr">
@@ -48812,7 +48248,7 @@
       </c>
       <c r="B1311" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C1311" s="13" t="inlineStr">
@@ -48836,7 +48272,7 @@
       </c>
       <c r="B1312" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C1312" s="13" t="inlineStr">
@@ -48860,7 +48296,7 @@
       </c>
       <c r="B1313" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C1313" s="13" t="inlineStr">
@@ -48884,7 +48320,7 @@
       </c>
       <c r="B1314" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C1314" s="13" t="inlineStr">
@@ -48908,7 +48344,7 @@
       </c>
       <c r="B1315" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C1315" s="13" t="inlineStr">
@@ -48932,7 +48368,7 @@
       </c>
       <c r="B1316" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C1316" s="13" t="inlineStr">
@@ -48956,7 +48392,7 @@
       </c>
       <c r="B1317" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C1317" s="13" t="inlineStr">
@@ -48980,7 +48416,7 @@
       </c>
       <c r="B1318" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C1318" s="13" t="inlineStr">
@@ -49004,7 +48440,7 @@
       </c>
       <c r="B1319" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C1319" s="13" t="inlineStr">
@@ -49028,7 +48464,7 @@
       </c>
       <c r="B1320" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C1320" s="13" t="inlineStr">
@@ -49052,7 +48488,7 @@
       </c>
       <c r="B1321" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C1321" s="13" t="inlineStr">
@@ -49076,7 +48512,7 @@
       </c>
       <c r="B1322" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C1322" s="13" t="inlineStr">
@@ -49100,7 +48536,7 @@
       </c>
       <c r="B1323" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C1323" s="13" t="inlineStr">
@@ -49124,7 +48560,7 @@
       </c>
       <c r="B1324" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C1324" s="13" t="inlineStr">
@@ -49148,7 +48584,7 @@
       </c>
       <c r="B1325" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C1325" s="13" t="inlineStr">
@@ -49172,7 +48608,7 @@
       </c>
       <c r="B1326" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C1326" s="13" t="inlineStr">
@@ -49196,7 +48632,7 @@
       </c>
       <c r="B1327" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C1327" s="13" t="inlineStr">
@@ -49220,7 +48656,7 @@
       </c>
       <c r="B1328" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C1328" s="13" t="inlineStr">
@@ -49244,7 +48680,7 @@
       </c>
       <c r="B1329" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C1329" s="13" t="inlineStr">
@@ -49268,7 +48704,7 @@
       </c>
       <c r="B1330" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C1330" s="13" t="inlineStr">
@@ -49292,7 +48728,7 @@
       </c>
       <c r="B1331" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C1331" s="13" t="inlineStr">
@@ -49316,7 +48752,7 @@
       </c>
       <c r="B1332" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C1332" s="13" t="inlineStr">
@@ -49340,7 +48776,7 @@
       </c>
       <c r="B1333" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C1333" s="13" t="inlineStr">
@@ -49364,7 +48800,7 @@
       </c>
       <c r="B1334" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C1334" s="13" t="inlineStr">
@@ -49388,7 +48824,7 @@
       </c>
       <c r="B1335" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C1335" s="13" t="inlineStr">
@@ -49412,7 +48848,7 @@
       </c>
       <c r="B1336" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C1336" s="13" t="inlineStr">
@@ -49436,7 +48872,7 @@
       </c>
       <c r="B1337" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C1337" s="13" t="inlineStr">
@@ -49460,7 +48896,7 @@
       </c>
       <c r="B1338" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C1338" s="13" t="inlineStr">
@@ -49484,7 +48920,7 @@
       </c>
       <c r="B1339" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C1339" s="13" t="inlineStr">
@@ -49508,7 +48944,7 @@
       </c>
       <c r="B1340" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C1340" s="13" t="inlineStr">
@@ -49532,7 +48968,7 @@
       </c>
       <c r="B1341" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C1341" s="13" t="inlineStr">
@@ -49556,7 +48992,7 @@
       </c>
       <c r="B1342" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C1342" s="13" t="inlineStr">
@@ -49580,7 +49016,7 @@
       </c>
       <c r="B1343" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C1343" s="13" t="inlineStr">
@@ -49604,7 +49040,7 @@
       </c>
       <c r="B1344" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C1344" s="13" t="inlineStr">
@@ -49628,7 +49064,7 @@
       </c>
       <c r="B1345" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C1345" s="13" t="inlineStr">
@@ -49652,7 +49088,7 @@
       </c>
       <c r="B1346" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C1346" s="13" t="inlineStr">
@@ -49676,7 +49112,7 @@
       </c>
       <c r="B1347" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C1347" s="13" t="inlineStr">
@@ -49700,7 +49136,7 @@
       </c>
       <c r="B1348" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C1348" s="13" t="inlineStr">
@@ -49724,7 +49160,7 @@
       </c>
       <c r="B1349" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C1349" s="13" t="inlineStr">
@@ -49748,7 +49184,7 @@
       </c>
       <c r="B1350" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C1350" s="13" t="inlineStr">
@@ -49772,7 +49208,7 @@
       </c>
       <c r="B1351" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C1351" s="13" t="inlineStr">
@@ -49796,7 +49232,7 @@
       </c>
       <c r="B1352" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C1352" s="13" t="inlineStr">
@@ -49820,7 +49256,7 @@
       </c>
       <c r="B1353" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C1353" s="13" t="inlineStr">
@@ -49844,7 +49280,7 @@
       </c>
       <c r="B1354" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C1354" s="13" t="inlineStr">
@@ -49868,7 +49304,7 @@
       </c>
       <c r="B1355" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C1355" s="13" t="inlineStr">
@@ -49892,7 +49328,7 @@
       </c>
       <c r="B1356" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C1356" s="13" t="inlineStr">
@@ -49916,7 +49352,7 @@
       </c>
       <c r="B1357" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C1357" s="13" t="inlineStr">
@@ -49940,7 +49376,7 @@
       </c>
       <c r="B1358" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C1358" s="13" t="inlineStr">
@@ -49964,7 +49400,7 @@
       </c>
       <c r="B1359" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C1359" s="13" t="inlineStr">
@@ -49988,7 +49424,7 @@
       </c>
       <c r="B1360" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C1360" s="13" t="inlineStr">
@@ -50012,7 +49448,7 @@
       </c>
       <c r="B1361" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C1361" s="13" t="inlineStr">
@@ -50036,7 +49472,7 @@
       </c>
       <c r="B1362" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C1362" s="13" t="inlineStr">
@@ -50060,7 +49496,7 @@
       </c>
       <c r="B1363" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C1363" s="13" t="inlineStr">
@@ -50084,7 +49520,7 @@
       </c>
       <c r="B1364" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C1364" s="13" t="inlineStr">
@@ -50108,7 +49544,7 @@
       </c>
       <c r="B1365" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C1365" s="13" t="inlineStr">
@@ -50132,7 +49568,7 @@
       </c>
       <c r="B1366" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C1366" s="13" t="inlineStr">
@@ -50156,7 +49592,7 @@
       </c>
       <c r="B1367" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C1367" s="13" t="inlineStr">
@@ -50180,7 +49616,7 @@
       </c>
       <c r="B1368" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C1368" s="13" t="inlineStr">
@@ -50204,7 +49640,7 @@
       </c>
       <c r="B1369" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C1369" s="13" t="inlineStr">
@@ -50228,7 +49664,7 @@
       </c>
       <c r="B1370" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C1370" s="13" t="inlineStr">
@@ -50252,7 +49688,7 @@
       </c>
       <c r="B1371" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C1371" s="13" t="inlineStr">
@@ -50276,7 +49712,7 @@
       </c>
       <c r="B1372" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C1372" s="13" t="inlineStr">
@@ -50300,7 +49736,7 @@
       </c>
       <c r="B1373" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C1373" s="13" t="inlineStr">
@@ -50324,7 +49760,7 @@
       </c>
       <c r="B1374" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C1374" s="13" t="inlineStr">
@@ -50348,7 +49784,7 @@
       </c>
       <c r="B1375" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C1375" s="13" t="inlineStr">
@@ -50372,7 +49808,7 @@
       </c>
       <c r="B1376" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C1376" s="13" t="inlineStr">
@@ -50396,7 +49832,7 @@
       </c>
       <c r="B1377" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C1377" s="13" t="inlineStr">
@@ -50420,7 +49856,7 @@
       </c>
       <c r="B1378" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C1378" s="13" t="inlineStr">
@@ -50444,7 +49880,7 @@
       </c>
       <c r="B1379" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C1379" s="13" t="inlineStr">
@@ -50468,7 +49904,7 @@
       </c>
       <c r="B1380" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C1380" s="13" t="inlineStr">
@@ -50492,7 +49928,7 @@
       </c>
       <c r="B1381" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C1381" s="13" t="inlineStr">
@@ -50516,7 +49952,7 @@
       </c>
       <c r="B1382" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C1382" s="13" t="inlineStr">
@@ -50540,7 +49976,7 @@
       </c>
       <c r="B1383" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C1383" s="13" t="inlineStr">
@@ -50564,7 +50000,7 @@
       </c>
       <c r="B1384" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C1384" s="13" t="inlineStr">
@@ -50588,7 +50024,7 @@
       </c>
       <c r="B1385" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C1385" s="13" t="inlineStr">
@@ -50612,7 +50048,7 @@
       </c>
       <c r="B1386" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C1386" s="13" t="inlineStr">
@@ -50636,7 +50072,7 @@
       </c>
       <c r="B1387" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C1387" s="13" t="inlineStr">
@@ -50660,7 +50096,7 @@
       </c>
       <c r="B1388" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C1388" s="13" t="inlineStr">
@@ -50684,7 +50120,7 @@
       </c>
       <c r="B1389" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C1389" s="13" t="inlineStr">
@@ -50708,7 +50144,7 @@
       </c>
       <c r="B1390" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C1390" s="13" t="inlineStr">
@@ -50732,7 +50168,7 @@
       </c>
       <c r="B1391" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C1391" s="13" t="inlineStr">
@@ -50756,7 +50192,7 @@
       </c>
       <c r="B1392" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C1392" s="13" t="inlineStr">
@@ -50780,7 +50216,7 @@
       </c>
       <c r="B1393" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C1393" s="13" t="inlineStr">
@@ -50804,7 +50240,7 @@
       </c>
       <c r="B1394" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C1394" s="13" t="inlineStr">
@@ -50828,7 +50264,7 @@
       </c>
       <c r="B1395" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C1395" s="13" t="inlineStr">
@@ -50852,7 +50288,7 @@
       </c>
       <c r="B1396" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C1396" s="13" t="inlineStr">
@@ -50876,7 +50312,7 @@
       </c>
       <c r="B1397" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C1397" s="13" t="inlineStr">
@@ -50900,7 +50336,7 @@
       </c>
       <c r="B1398" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C1398" s="13" t="inlineStr">
@@ -50924,7 +50360,7 @@
       </c>
       <c r="B1399" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C1399" s="13" t="inlineStr">
@@ -50948,7 +50384,7 @@
       </c>
       <c r="B1400" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C1400" s="13" t="inlineStr">
@@ -50972,7 +50408,7 @@
       </c>
       <c r="B1401" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C1401" s="13" t="inlineStr">
@@ -50996,7 +50432,7 @@
       </c>
       <c r="B1402" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C1402" s="13" t="inlineStr">
@@ -51020,7 +50456,7 @@
       </c>
       <c r="B1403" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C1403" s="13" t="inlineStr">
@@ -51044,7 +50480,7 @@
       </c>
       <c r="B1404" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C1404" s="13" t="inlineStr">
@@ -51068,7 +50504,7 @@
       </c>
       <c r="B1405" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C1405" s="13" t="inlineStr">
@@ -51092,7 +50528,7 @@
       </c>
       <c r="B1406" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C1406" s="13" t="inlineStr">
@@ -51116,7 +50552,7 @@
       </c>
       <c r="B1407" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C1407" s="13" t="inlineStr">
@@ -51140,7 +50576,7 @@
       </c>
       <c r="B1408" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C1408" s="13" t="inlineStr">
@@ -51164,7 +50600,7 @@
       </c>
       <c r="B1409" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C1409" s="13" t="inlineStr">
@@ -51188,7 +50624,7 @@
       </c>
       <c r="B1410" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C1410" s="13" t="inlineStr">
@@ -51212,7 +50648,7 @@
       </c>
       <c r="B1411" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C1411" s="13" t="inlineStr">
@@ -51236,7 +50672,7 @@
       </c>
       <c r="B1412" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C1412" s="13" t="inlineStr">
@@ -51260,7 +50696,7 @@
       </c>
       <c r="B1413" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C1413" s="13" t="inlineStr">
@@ -51284,7 +50720,7 @@
       </c>
       <c r="B1414" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C1414" s="13" t="inlineStr">
@@ -51308,7 +50744,7 @@
       </c>
       <c r="B1415" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C1415" s="13" t="inlineStr">
@@ -51332,7 +50768,7 @@
       </c>
       <c r="B1416" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C1416" s="13" t="inlineStr">
@@ -51356,7 +50792,7 @@
       </c>
       <c r="B1417" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C1417" s="13" t="inlineStr">
@@ -51380,7 +50816,7 @@
       </c>
       <c r="B1418" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C1418" s="13" t="inlineStr">
@@ -51404,7 +50840,7 @@
       </c>
       <c r="B1419" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C1419" s="13" t="inlineStr">
@@ -51428,7 +50864,7 @@
       </c>
       <c r="B1420" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C1420" s="13" t="inlineStr">
@@ -51452,7 +50888,7 @@
       </c>
       <c r="B1421" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C1421" s="13" t="inlineStr">
@@ -51476,7 +50912,7 @@
       </c>
       <c r="B1422" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C1422" s="13" t="inlineStr">
@@ -51500,7 +50936,7 @@
       </c>
       <c r="B1423" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C1423" s="13" t="inlineStr">
@@ -51524,7 +50960,7 @@
       </c>
       <c r="B1424" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C1424" s="13" t="inlineStr">
@@ -51548,7 +50984,7 @@
       </c>
       <c r="B1425" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C1425" s="13" t="inlineStr">
@@ -51572,7 +51008,7 @@
       </c>
       <c r="B1426" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C1426" s="13" t="inlineStr">
@@ -51596,7 +51032,7 @@
       </c>
       <c r="B1427" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C1427" s="13" t="inlineStr">
@@ -51620,7 +51056,7 @@
       </c>
       <c r="B1428" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C1428" s="13" t="inlineStr">
@@ -51644,7 +51080,7 @@
       </c>
       <c r="B1429" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C1429" s="13" t="inlineStr">
@@ -51668,7 +51104,7 @@
       </c>
       <c r="B1430" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C1430" s="13" t="inlineStr">
@@ -51692,7 +51128,7 @@
       </c>
       <c r="B1431" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C1431" s="13" t="inlineStr">
@@ -51716,7 +51152,7 @@
       </c>
       <c r="B1432" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C1432" s="13" t="inlineStr">
@@ -51740,7 +51176,7 @@
       </c>
       <c r="B1433" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C1433" s="13" t="inlineStr">
@@ -51764,7 +51200,7 @@
       </c>
       <c r="B1434" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C1434" s="13" t="inlineStr">
@@ -51788,7 +51224,7 @@
       </c>
       <c r="B1435" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C1435" s="13" t="inlineStr">
@@ -51812,7 +51248,7 @@
       </c>
       <c r="B1436" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C1436" s="13" t="inlineStr">
@@ -51836,7 +51272,7 @@
       </c>
       <c r="B1437" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C1437" s="13" t="inlineStr">
@@ -51860,7 +51296,7 @@
       </c>
       <c r="B1438" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C1438" s="13" t="inlineStr">
@@ -51884,7 +51320,7 @@
       </c>
       <c r="B1439" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C1439" s="13" t="inlineStr">
@@ -51908,7 +51344,7 @@
       </c>
       <c r="B1440" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C1440" s="13" t="inlineStr">
@@ -51932,7 +51368,7 @@
       </c>
       <c r="B1441" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C1441" s="13" t="inlineStr">
@@ -51956,7 +51392,7 @@
       </c>
       <c r="B1442" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C1442" s="13" t="inlineStr">
@@ -51980,7 +51416,7 @@
       </c>
       <c r="B1443" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C1443" s="13" t="inlineStr">
@@ -52004,7 +51440,7 @@
       </c>
       <c r="B1444" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C1444" s="13" t="inlineStr">
@@ -52028,7 +51464,7 @@
       </c>
       <c r="B1445" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C1445" s="13" t="inlineStr">
@@ -52052,7 +51488,7 @@
       </c>
       <c r="B1446" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C1446" s="13" t="inlineStr">
@@ -52076,7 +51512,7 @@
       </c>
       <c r="B1447" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C1447" s="13" t="inlineStr">
@@ -52100,7 +51536,7 @@
       </c>
       <c r="B1448" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C1448" s="13" t="inlineStr">
@@ -52124,7 +51560,7 @@
       </c>
       <c r="B1449" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C1449" s="13" t="inlineStr">
@@ -52148,7 +51584,7 @@
       </c>
       <c r="B1450" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C1450" s="13" t="inlineStr">
@@ -52172,7 +51608,7 @@
       </c>
       <c r="B1451" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C1451" s="13" t="inlineStr">
@@ -52196,7 +51632,7 @@
       </c>
       <c r="B1452" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C1452" s="13" t="inlineStr">
@@ -52220,7 +51656,7 @@
       </c>
       <c r="B1453" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C1453" s="13" t="inlineStr">
@@ -52244,7 +51680,7 @@
       </c>
       <c r="B1454" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C1454" s="13" t="inlineStr">
@@ -52268,7 +51704,7 @@
       </c>
       <c r="B1455" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C1455" s="13" t="inlineStr">
@@ -52292,7 +51728,7 @@
       </c>
       <c r="B1456" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C1456" s="13" t="inlineStr">
@@ -52316,7 +51752,7 @@
       </c>
       <c r="B1457" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C1457" s="13" t="inlineStr">
@@ -52340,7 +51776,7 @@
       </c>
       <c r="B1458" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C1458" s="13" t="inlineStr">
@@ -52364,7 +51800,7 @@
       </c>
       <c r="B1459" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C1459" s="13" t="inlineStr">
@@ -52388,7 +51824,7 @@
       </c>
       <c r="B1460" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C1460" s="13" t="inlineStr">
@@ -52412,7 +51848,7 @@
       </c>
       <c r="B1461" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C1461" s="13" t="inlineStr">
@@ -52436,7 +51872,7 @@
       </c>
       <c r="B1462" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C1462" s="13" t="inlineStr">
@@ -52460,7 +51896,7 @@
       </c>
       <c r="B1463" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C1463" s="13" t="inlineStr">
@@ -52484,7 +51920,7 @@
       </c>
       <c r="B1464" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C1464" s="13" t="inlineStr">
@@ -52508,7 +51944,7 @@
       </c>
       <c r="B1465" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C1465" s="13" t="inlineStr">
@@ -52532,7 +51968,7 @@
       </c>
       <c r="B1466" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C1466" s="13" t="inlineStr">
@@ -52556,7 +51992,7 @@
       </c>
       <c r="B1467" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C1467" s="13" t="inlineStr">
@@ -52580,7 +52016,7 @@
       </c>
       <c r="B1468" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C1468" s="13" t="inlineStr">
@@ -52604,7 +52040,7 @@
       </c>
       <c r="B1469" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C1469" s="13" t="inlineStr">
@@ -52628,7 +52064,7 @@
       </c>
       <c r="B1470" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C1470" s="13" t="inlineStr">
@@ -52652,7 +52088,7 @@
       </c>
       <c r="B1471" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C1471" s="13" t="inlineStr">
@@ -52676,7 +52112,7 @@
       </c>
       <c r="B1472" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C1472" s="13" t="inlineStr">
@@ -52700,7 +52136,7 @@
       </c>
       <c r="B1473" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C1473" s="13" t="inlineStr">
@@ -52724,7 +52160,7 @@
       </c>
       <c r="B1474" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C1474" s="13" t="inlineStr">
@@ -52748,7 +52184,7 @@
       </c>
       <c r="B1475" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C1475" s="13" t="inlineStr">
@@ -52772,7 +52208,7 @@
       </c>
       <c r="B1476" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C1476" s="13" t="inlineStr">
@@ -52796,7 +52232,7 @@
       </c>
       <c r="B1477" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C1477" s="13" t="inlineStr">
@@ -52820,7 +52256,7 @@
       </c>
       <c r="B1478" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C1478" s="13" t="inlineStr">
@@ -52844,7 +52280,7 @@
       </c>
       <c r="B1479" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C1479" s="13" t="inlineStr">
@@ -52868,7 +52304,7 @@
       </c>
       <c r="B1480" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C1480" s="13" t="inlineStr">
@@ -52892,7 +52328,7 @@
       </c>
       <c r="B1481" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C1481" s="13" t="inlineStr">
@@ -52907,1446 +52343,6 @@
       <c r="H1481" s="6" t="inlineStr"/>
       <c r="I1481" s="6" t="inlineStr"/>
       <c r="J1481" s="6" t="inlineStr"/>
-    </row>
-    <row r="1482" ht="40" customHeight="1">
-      <c r="A1482" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B1482" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C1482" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1482" s="6" t="inlineStr"/>
-      <c r="E1482" s="6" t="inlineStr"/>
-      <c r="F1482" s="6" t="inlineStr"/>
-      <c r="G1482" s="6" t="inlineStr"/>
-      <c r="H1482" s="6" t="inlineStr"/>
-      <c r="I1482" s="6" t="inlineStr"/>
-      <c r="J1482" s="6" t="inlineStr"/>
-    </row>
-    <row r="1483" ht="40" customHeight="1">
-      <c r="A1483" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B1483" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C1483" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1483" s="6" t="inlineStr"/>
-      <c r="E1483" s="6" t="inlineStr"/>
-      <c r="F1483" s="6" t="inlineStr"/>
-      <c r="G1483" s="6" t="inlineStr"/>
-      <c r="H1483" s="6" t="inlineStr"/>
-      <c r="I1483" s="6" t="inlineStr"/>
-      <c r="J1483" s="6" t="inlineStr"/>
-    </row>
-    <row r="1484" ht="40" customHeight="1">
-      <c r="A1484" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B1484" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C1484" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1484" s="6" t="inlineStr"/>
-      <c r="E1484" s="6" t="inlineStr"/>
-      <c r="F1484" s="6" t="inlineStr"/>
-      <c r="G1484" s="6" t="inlineStr"/>
-      <c r="H1484" s="6" t="inlineStr"/>
-      <c r="I1484" s="6" t="inlineStr"/>
-      <c r="J1484" s="6" t="inlineStr"/>
-    </row>
-    <row r="1485" ht="40" customHeight="1">
-      <c r="A1485" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B1485" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C1485" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1485" s="6" t="inlineStr"/>
-      <c r="E1485" s="6" t="inlineStr"/>
-      <c r="F1485" s="6" t="inlineStr"/>
-      <c r="G1485" s="6" t="inlineStr"/>
-      <c r="H1485" s="6" t="inlineStr"/>
-      <c r="I1485" s="6" t="inlineStr"/>
-      <c r="J1485" s="6" t="inlineStr"/>
-    </row>
-    <row r="1486" ht="40" customHeight="1">
-      <c r="A1486" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B1486" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C1486" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1486" s="6" t="inlineStr"/>
-      <c r="E1486" s="6" t="inlineStr"/>
-      <c r="F1486" s="6" t="inlineStr"/>
-      <c r="G1486" s="6" t="inlineStr"/>
-      <c r="H1486" s="6" t="inlineStr"/>
-      <c r="I1486" s="6" t="inlineStr"/>
-      <c r="J1486" s="6" t="inlineStr"/>
-    </row>
-    <row r="1487" ht="40" customHeight="1">
-      <c r="A1487" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B1487" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C1487" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1487" s="6" t="inlineStr"/>
-      <c r="E1487" s="6" t="inlineStr"/>
-      <c r="F1487" s="6" t="inlineStr"/>
-      <c r="G1487" s="6" t="inlineStr"/>
-      <c r="H1487" s="6" t="inlineStr"/>
-      <c r="I1487" s="6" t="inlineStr"/>
-      <c r="J1487" s="6" t="inlineStr"/>
-    </row>
-    <row r="1488" ht="40" customHeight="1">
-      <c r="A1488" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B1488" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C1488" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1488" s="6" t="inlineStr"/>
-      <c r="E1488" s="6" t="inlineStr"/>
-      <c r="F1488" s="6" t="inlineStr"/>
-      <c r="G1488" s="6" t="inlineStr"/>
-      <c r="H1488" s="6" t="inlineStr"/>
-      <c r="I1488" s="6" t="inlineStr"/>
-      <c r="J1488" s="6" t="inlineStr"/>
-    </row>
-    <row r="1489" ht="40" customHeight="1">
-      <c r="A1489" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B1489" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C1489" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1489" s="6" t="inlineStr"/>
-      <c r="E1489" s="6" t="inlineStr"/>
-      <c r="F1489" s="6" t="inlineStr"/>
-      <c r="G1489" s="6" t="inlineStr"/>
-      <c r="H1489" s="6" t="inlineStr"/>
-      <c r="I1489" s="6" t="inlineStr"/>
-      <c r="J1489" s="6" t="inlineStr"/>
-    </row>
-    <row r="1490" ht="40" customHeight="1">
-      <c r="A1490" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B1490" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C1490" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1490" s="6" t="inlineStr"/>
-      <c r="E1490" s="6" t="inlineStr"/>
-      <c r="F1490" s="6" t="inlineStr"/>
-      <c r="G1490" s="6" t="inlineStr"/>
-      <c r="H1490" s="6" t="inlineStr"/>
-      <c r="I1490" s="6" t="inlineStr"/>
-      <c r="J1490" s="6" t="inlineStr"/>
-    </row>
-    <row r="1491" ht="40" customHeight="1">
-      <c r="A1491" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B1491" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C1491" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1491" s="6" t="inlineStr"/>
-      <c r="E1491" s="6" t="inlineStr"/>
-      <c r="F1491" s="6" t="inlineStr"/>
-      <c r="G1491" s="6" t="inlineStr"/>
-      <c r="H1491" s="6" t="inlineStr"/>
-      <c r="I1491" s="6" t="inlineStr"/>
-      <c r="J1491" s="6" t="inlineStr"/>
-    </row>
-    <row r="1492" ht="40" customHeight="1">
-      <c r="A1492" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B1492" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C1492" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1492" s="6" t="inlineStr"/>
-      <c r="E1492" s="6" t="inlineStr"/>
-      <c r="F1492" s="6" t="inlineStr"/>
-      <c r="G1492" s="6" t="inlineStr"/>
-      <c r="H1492" s="6" t="inlineStr"/>
-      <c r="I1492" s="6" t="inlineStr"/>
-      <c r="J1492" s="6" t="inlineStr"/>
-    </row>
-    <row r="1493" ht="40" customHeight="1">
-      <c r="A1493" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B1493" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C1493" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1493" s="6" t="inlineStr"/>
-      <c r="E1493" s="6" t="inlineStr"/>
-      <c r="F1493" s="6" t="inlineStr"/>
-      <c r="G1493" s="6" t="inlineStr"/>
-      <c r="H1493" s="6" t="inlineStr"/>
-      <c r="I1493" s="6" t="inlineStr"/>
-      <c r="J1493" s="6" t="inlineStr"/>
-    </row>
-    <row r="1494" ht="40" customHeight="1">
-      <c r="A1494" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B1494" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C1494" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1494" s="6" t="inlineStr"/>
-      <c r="E1494" s="6" t="inlineStr"/>
-      <c r="F1494" s="6" t="inlineStr"/>
-      <c r="G1494" s="6" t="inlineStr"/>
-      <c r="H1494" s="6" t="inlineStr"/>
-      <c r="I1494" s="6" t="inlineStr"/>
-      <c r="J1494" s="6" t="inlineStr"/>
-    </row>
-    <row r="1495" ht="40" customHeight="1">
-      <c r="A1495" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B1495" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C1495" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1495" s="6" t="inlineStr"/>
-      <c r="E1495" s="6" t="inlineStr"/>
-      <c r="F1495" s="6" t="inlineStr"/>
-      <c r="G1495" s="6" t="inlineStr"/>
-      <c r="H1495" s="6" t="inlineStr"/>
-      <c r="I1495" s="6" t="inlineStr"/>
-      <c r="J1495" s="6" t="inlineStr"/>
-    </row>
-    <row r="1496" ht="40" customHeight="1">
-      <c r="A1496" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B1496" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C1496" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1496" s="6" t="inlineStr"/>
-      <c r="E1496" s="6" t="inlineStr"/>
-      <c r="F1496" s="6" t="inlineStr"/>
-      <c r="G1496" s="6" t="inlineStr"/>
-      <c r="H1496" s="6" t="inlineStr"/>
-      <c r="I1496" s="6" t="inlineStr"/>
-      <c r="J1496" s="6" t="inlineStr"/>
-    </row>
-    <row r="1497" ht="40" customHeight="1">
-      <c r="A1497" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B1497" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C1497" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1497" s="6" t="inlineStr"/>
-      <c r="E1497" s="6" t="inlineStr"/>
-      <c r="F1497" s="6" t="inlineStr"/>
-      <c r="G1497" s="6" t="inlineStr"/>
-      <c r="H1497" s="6" t="inlineStr"/>
-      <c r="I1497" s="6" t="inlineStr"/>
-      <c r="J1497" s="6" t="inlineStr"/>
-    </row>
-    <row r="1498" ht="40" customHeight="1">
-      <c r="A1498" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B1498" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C1498" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1498" s="6" t="inlineStr"/>
-      <c r="E1498" s="6" t="inlineStr"/>
-      <c r="F1498" s="6" t="inlineStr"/>
-      <c r="G1498" s="6" t="inlineStr"/>
-      <c r="H1498" s="6" t="inlineStr"/>
-      <c r="I1498" s="6" t="inlineStr"/>
-      <c r="J1498" s="6" t="inlineStr"/>
-    </row>
-    <row r="1499" ht="40" customHeight="1">
-      <c r="A1499" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B1499" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C1499" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1499" s="6" t="inlineStr"/>
-      <c r="E1499" s="6" t="inlineStr"/>
-      <c r="F1499" s="6" t="inlineStr"/>
-      <c r="G1499" s="6" t="inlineStr"/>
-      <c r="H1499" s="6" t="inlineStr"/>
-      <c r="I1499" s="6" t="inlineStr"/>
-      <c r="J1499" s="6" t="inlineStr"/>
-    </row>
-    <row r="1500" ht="40" customHeight="1">
-      <c r="A1500" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B1500" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C1500" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1500" s="6" t="inlineStr"/>
-      <c r="E1500" s="6" t="inlineStr"/>
-      <c r="F1500" s="6" t="inlineStr"/>
-      <c r="G1500" s="6" t="inlineStr"/>
-      <c r="H1500" s="6" t="inlineStr"/>
-      <c r="I1500" s="6" t="inlineStr"/>
-      <c r="J1500" s="6" t="inlineStr"/>
-    </row>
-    <row r="1501" ht="40" customHeight="1">
-      <c r="A1501" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B1501" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C1501" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1501" s="6" t="inlineStr"/>
-      <c r="E1501" s="6" t="inlineStr"/>
-      <c r="F1501" s="6" t="inlineStr"/>
-      <c r="G1501" s="6" t="inlineStr"/>
-      <c r="H1501" s="6" t="inlineStr"/>
-      <c r="I1501" s="6" t="inlineStr"/>
-      <c r="J1501" s="6" t="inlineStr"/>
-    </row>
-    <row r="1502" ht="40" customHeight="1">
-      <c r="A1502" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B1502" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C1502" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1502" s="6" t="inlineStr"/>
-      <c r="E1502" s="6" t="inlineStr"/>
-      <c r="F1502" s="6" t="inlineStr"/>
-      <c r="G1502" s="6" t="inlineStr"/>
-      <c r="H1502" s="6" t="inlineStr"/>
-      <c r="I1502" s="6" t="inlineStr"/>
-      <c r="J1502" s="6" t="inlineStr"/>
-    </row>
-    <row r="1503" ht="40" customHeight="1">
-      <c r="A1503" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B1503" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C1503" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1503" s="6" t="inlineStr"/>
-      <c r="E1503" s="6" t="inlineStr"/>
-      <c r="F1503" s="6" t="inlineStr"/>
-      <c r="G1503" s="6" t="inlineStr"/>
-      <c r="H1503" s="6" t="inlineStr"/>
-      <c r="I1503" s="6" t="inlineStr"/>
-      <c r="J1503" s="6" t="inlineStr"/>
-    </row>
-    <row r="1504" ht="40" customHeight="1">
-      <c r="A1504" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B1504" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C1504" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1504" s="6" t="inlineStr"/>
-      <c r="E1504" s="6" t="inlineStr"/>
-      <c r="F1504" s="6" t="inlineStr"/>
-      <c r="G1504" s="6" t="inlineStr"/>
-      <c r="H1504" s="6" t="inlineStr"/>
-      <c r="I1504" s="6" t="inlineStr"/>
-      <c r="J1504" s="6" t="inlineStr"/>
-    </row>
-    <row r="1505" ht="40" customHeight="1">
-      <c r="A1505" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B1505" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C1505" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1505" s="6" t="inlineStr"/>
-      <c r="E1505" s="6" t="inlineStr"/>
-      <c r="F1505" s="6" t="inlineStr"/>
-      <c r="G1505" s="6" t="inlineStr"/>
-      <c r="H1505" s="6" t="inlineStr"/>
-      <c r="I1505" s="6" t="inlineStr"/>
-      <c r="J1505" s="6" t="inlineStr"/>
-    </row>
-    <row r="1506" ht="40" customHeight="1">
-      <c r="A1506" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B1506" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C1506" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1506" s="6" t="inlineStr"/>
-      <c r="E1506" s="6" t="inlineStr"/>
-      <c r="F1506" s="6" t="inlineStr"/>
-      <c r="G1506" s="6" t="inlineStr"/>
-      <c r="H1506" s="6" t="inlineStr"/>
-      <c r="I1506" s="6" t="inlineStr"/>
-      <c r="J1506" s="6" t="inlineStr"/>
-    </row>
-    <row r="1507" ht="40" customHeight="1">
-      <c r="A1507" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B1507" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C1507" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1507" s="6" t="inlineStr"/>
-      <c r="E1507" s="6" t="inlineStr"/>
-      <c r="F1507" s="6" t="inlineStr"/>
-      <c r="G1507" s="6" t="inlineStr"/>
-      <c r="H1507" s="6" t="inlineStr"/>
-      <c r="I1507" s="6" t="inlineStr"/>
-      <c r="J1507" s="6" t="inlineStr"/>
-    </row>
-    <row r="1508" ht="40" customHeight="1">
-      <c r="A1508" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B1508" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C1508" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1508" s="6" t="inlineStr"/>
-      <c r="E1508" s="6" t="inlineStr"/>
-      <c r="F1508" s="6" t="inlineStr"/>
-      <c r="G1508" s="6" t="inlineStr"/>
-      <c r="H1508" s="6" t="inlineStr"/>
-      <c r="I1508" s="6" t="inlineStr"/>
-      <c r="J1508" s="6" t="inlineStr"/>
-    </row>
-    <row r="1509" ht="40" customHeight="1">
-      <c r="A1509" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B1509" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C1509" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1509" s="6" t="inlineStr"/>
-      <c r="E1509" s="6" t="inlineStr"/>
-      <c r="F1509" s="6" t="inlineStr"/>
-      <c r="G1509" s="6" t="inlineStr"/>
-      <c r="H1509" s="6" t="inlineStr"/>
-      <c r="I1509" s="6" t="inlineStr"/>
-      <c r="J1509" s="6" t="inlineStr"/>
-    </row>
-    <row r="1510" ht="40" customHeight="1">
-      <c r="A1510" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B1510" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C1510" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1510" s="6" t="inlineStr"/>
-      <c r="E1510" s="6" t="inlineStr"/>
-      <c r="F1510" s="6" t="inlineStr"/>
-      <c r="G1510" s="6" t="inlineStr"/>
-      <c r="H1510" s="6" t="inlineStr"/>
-      <c r="I1510" s="6" t="inlineStr"/>
-      <c r="J1510" s="6" t="inlineStr"/>
-    </row>
-    <row r="1511" ht="40" customHeight="1">
-      <c r="A1511" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B1511" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C1511" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1511" s="6" t="inlineStr"/>
-      <c r="E1511" s="6" t="inlineStr"/>
-      <c r="F1511" s="6" t="inlineStr"/>
-      <c r="G1511" s="6" t="inlineStr"/>
-      <c r="H1511" s="6" t="inlineStr"/>
-      <c r="I1511" s="6" t="inlineStr"/>
-      <c r="J1511" s="6" t="inlineStr"/>
-    </row>
-    <row r="1512" ht="40" customHeight="1">
-      <c r="A1512" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B1512" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C1512" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1512" s="6" t="inlineStr"/>
-      <c r="E1512" s="6" t="inlineStr"/>
-      <c r="F1512" s="6" t="inlineStr"/>
-      <c r="G1512" s="6" t="inlineStr"/>
-      <c r="H1512" s="6" t="inlineStr"/>
-      <c r="I1512" s="6" t="inlineStr"/>
-      <c r="J1512" s="6" t="inlineStr"/>
-    </row>
-    <row r="1513" ht="40" customHeight="1">
-      <c r="A1513" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B1513" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C1513" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1513" s="6" t="inlineStr"/>
-      <c r="E1513" s="6" t="inlineStr"/>
-      <c r="F1513" s="6" t="inlineStr"/>
-      <c r="G1513" s="6" t="inlineStr"/>
-      <c r="H1513" s="6" t="inlineStr"/>
-      <c r="I1513" s="6" t="inlineStr"/>
-      <c r="J1513" s="6" t="inlineStr"/>
-    </row>
-    <row r="1514" ht="40" customHeight="1">
-      <c r="A1514" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B1514" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C1514" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1514" s="6" t="inlineStr"/>
-      <c r="E1514" s="6" t="inlineStr"/>
-      <c r="F1514" s="6" t="inlineStr"/>
-      <c r="G1514" s="6" t="inlineStr"/>
-      <c r="H1514" s="6" t="inlineStr"/>
-      <c r="I1514" s="6" t="inlineStr"/>
-      <c r="J1514" s="6" t="inlineStr"/>
-    </row>
-    <row r="1515" ht="40" customHeight="1">
-      <c r="A1515" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B1515" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C1515" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1515" s="6" t="inlineStr"/>
-      <c r="E1515" s="6" t="inlineStr"/>
-      <c r="F1515" s="6" t="inlineStr"/>
-      <c r="G1515" s="6" t="inlineStr"/>
-      <c r="H1515" s="6" t="inlineStr"/>
-      <c r="I1515" s="6" t="inlineStr"/>
-      <c r="J1515" s="6" t="inlineStr"/>
-    </row>
-    <row r="1516" ht="40" customHeight="1">
-      <c r="A1516" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B1516" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C1516" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1516" s="6" t="inlineStr"/>
-      <c r="E1516" s="6" t="inlineStr"/>
-      <c r="F1516" s="6" t="inlineStr"/>
-      <c r="G1516" s="6" t="inlineStr"/>
-      <c r="H1516" s="6" t="inlineStr"/>
-      <c r="I1516" s="6" t="inlineStr"/>
-      <c r="J1516" s="6" t="inlineStr"/>
-    </row>
-    <row r="1517" ht="40" customHeight="1">
-      <c r="A1517" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B1517" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C1517" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1517" s="6" t="inlineStr"/>
-      <c r="E1517" s="6" t="inlineStr"/>
-      <c r="F1517" s="6" t="inlineStr"/>
-      <c r="G1517" s="6" t="inlineStr"/>
-      <c r="H1517" s="6" t="inlineStr"/>
-      <c r="I1517" s="6" t="inlineStr"/>
-      <c r="J1517" s="6" t="inlineStr"/>
-    </row>
-    <row r="1518" ht="40" customHeight="1">
-      <c r="A1518" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B1518" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C1518" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1518" s="6" t="inlineStr"/>
-      <c r="E1518" s="6" t="inlineStr"/>
-      <c r="F1518" s="6" t="inlineStr"/>
-      <c r="G1518" s="6" t="inlineStr"/>
-      <c r="H1518" s="6" t="inlineStr"/>
-      <c r="I1518" s="6" t="inlineStr"/>
-      <c r="J1518" s="6" t="inlineStr"/>
-    </row>
-    <row r="1519" ht="40" customHeight="1">
-      <c r="A1519" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B1519" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C1519" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1519" s="6" t="inlineStr"/>
-      <c r="E1519" s="6" t="inlineStr"/>
-      <c r="F1519" s="6" t="inlineStr"/>
-      <c r="G1519" s="6" t="inlineStr"/>
-      <c r="H1519" s="6" t="inlineStr"/>
-      <c r="I1519" s="6" t="inlineStr"/>
-      <c r="J1519" s="6" t="inlineStr"/>
-    </row>
-    <row r="1520" ht="40" customHeight="1">
-      <c r="A1520" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B1520" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C1520" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1520" s="6" t="inlineStr"/>
-      <c r="E1520" s="6" t="inlineStr"/>
-      <c r="F1520" s="6" t="inlineStr"/>
-      <c r="G1520" s="6" t="inlineStr"/>
-      <c r="H1520" s="6" t="inlineStr"/>
-      <c r="I1520" s="6" t="inlineStr"/>
-      <c r="J1520" s="6" t="inlineStr"/>
-    </row>
-    <row r="1521" ht="40" customHeight="1">
-      <c r="A1521" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B1521" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C1521" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1521" s="6" t="inlineStr"/>
-      <c r="E1521" s="6" t="inlineStr"/>
-      <c r="F1521" s="6" t="inlineStr"/>
-      <c r="G1521" s="6" t="inlineStr"/>
-      <c r="H1521" s="6" t="inlineStr"/>
-      <c r="I1521" s="6" t="inlineStr"/>
-      <c r="J1521" s="6" t="inlineStr"/>
-    </row>
-    <row r="1522" ht="40" customHeight="1">
-      <c r="A1522" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B1522" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C1522" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1522" s="6" t="inlineStr"/>
-      <c r="E1522" s="6" t="inlineStr"/>
-      <c r="F1522" s="6" t="inlineStr"/>
-      <c r="G1522" s="6" t="inlineStr"/>
-      <c r="H1522" s="6" t="inlineStr"/>
-      <c r="I1522" s="6" t="inlineStr"/>
-      <c r="J1522" s="6" t="inlineStr"/>
-    </row>
-    <row r="1523" ht="40" customHeight="1">
-      <c r="A1523" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B1523" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C1523" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1523" s="6" t="inlineStr"/>
-      <c r="E1523" s="6" t="inlineStr"/>
-      <c r="F1523" s="6" t="inlineStr"/>
-      <c r="G1523" s="6" t="inlineStr"/>
-      <c r="H1523" s="6" t="inlineStr"/>
-      <c r="I1523" s="6" t="inlineStr"/>
-      <c r="J1523" s="6" t="inlineStr"/>
-    </row>
-    <row r="1524" ht="40" customHeight="1">
-      <c r="A1524" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B1524" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C1524" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1524" s="6" t="inlineStr"/>
-      <c r="E1524" s="6" t="inlineStr"/>
-      <c r="F1524" s="6" t="inlineStr"/>
-      <c r="G1524" s="6" t="inlineStr"/>
-      <c r="H1524" s="6" t="inlineStr"/>
-      <c r="I1524" s="6" t="inlineStr"/>
-      <c r="J1524" s="6" t="inlineStr"/>
-    </row>
-    <row r="1525" ht="40" customHeight="1">
-      <c r="A1525" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B1525" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C1525" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1525" s="6" t="inlineStr"/>
-      <c r="E1525" s="6" t="inlineStr"/>
-      <c r="F1525" s="6" t="inlineStr"/>
-      <c r="G1525" s="6" t="inlineStr"/>
-      <c r="H1525" s="6" t="inlineStr"/>
-      <c r="I1525" s="6" t="inlineStr"/>
-      <c r="J1525" s="6" t="inlineStr"/>
-    </row>
-    <row r="1526" ht="40" customHeight="1">
-      <c r="A1526" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B1526" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C1526" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1526" s="6" t="inlineStr"/>
-      <c r="E1526" s="6" t="inlineStr"/>
-      <c r="F1526" s="6" t="inlineStr"/>
-      <c r="G1526" s="6" t="inlineStr"/>
-      <c r="H1526" s="6" t="inlineStr"/>
-      <c r="I1526" s="6" t="inlineStr"/>
-      <c r="J1526" s="6" t="inlineStr"/>
-    </row>
-    <row r="1527" ht="40" customHeight="1">
-      <c r="A1527" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B1527" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C1527" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1527" s="6" t="inlineStr"/>
-      <c r="E1527" s="6" t="inlineStr"/>
-      <c r="F1527" s="6" t="inlineStr"/>
-      <c r="G1527" s="6" t="inlineStr"/>
-      <c r="H1527" s="6" t="inlineStr"/>
-      <c r="I1527" s="6" t="inlineStr"/>
-      <c r="J1527" s="6" t="inlineStr"/>
-    </row>
-    <row r="1528" ht="40" customHeight="1">
-      <c r="A1528" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B1528" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C1528" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1528" s="6" t="inlineStr"/>
-      <c r="E1528" s="6" t="inlineStr"/>
-      <c r="F1528" s="6" t="inlineStr"/>
-      <c r="G1528" s="6" t="inlineStr"/>
-      <c r="H1528" s="6" t="inlineStr"/>
-      <c r="I1528" s="6" t="inlineStr"/>
-      <c r="J1528" s="6" t="inlineStr"/>
-    </row>
-    <row r="1529" ht="40" customHeight="1">
-      <c r="A1529" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B1529" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C1529" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1529" s="6" t="inlineStr"/>
-      <c r="E1529" s="6" t="inlineStr"/>
-      <c r="F1529" s="6" t="inlineStr"/>
-      <c r="G1529" s="6" t="inlineStr"/>
-      <c r="H1529" s="6" t="inlineStr"/>
-      <c r="I1529" s="6" t="inlineStr"/>
-      <c r="J1529" s="6" t="inlineStr"/>
-    </row>
-    <row r="1530" ht="40" customHeight="1">
-      <c r="A1530" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B1530" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C1530" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1530" s="6" t="inlineStr"/>
-      <c r="E1530" s="6" t="inlineStr"/>
-      <c r="F1530" s="6" t="inlineStr"/>
-      <c r="G1530" s="6" t="inlineStr"/>
-      <c r="H1530" s="6" t="inlineStr"/>
-      <c r="I1530" s="6" t="inlineStr"/>
-      <c r="J1530" s="6" t="inlineStr"/>
-    </row>
-    <row r="1531" ht="40" customHeight="1">
-      <c r="A1531" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B1531" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C1531" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1531" s="6" t="inlineStr"/>
-      <c r="E1531" s="6" t="inlineStr"/>
-      <c r="F1531" s="6" t="inlineStr"/>
-      <c r="G1531" s="6" t="inlineStr"/>
-      <c r="H1531" s="6" t="inlineStr"/>
-      <c r="I1531" s="6" t="inlineStr"/>
-      <c r="J1531" s="6" t="inlineStr"/>
-    </row>
-    <row r="1532" ht="40" customHeight="1">
-      <c r="A1532" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B1532" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C1532" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1532" s="6" t="inlineStr"/>
-      <c r="E1532" s="6" t="inlineStr"/>
-      <c r="F1532" s="6" t="inlineStr"/>
-      <c r="G1532" s="6" t="inlineStr"/>
-      <c r="H1532" s="6" t="inlineStr"/>
-      <c r="I1532" s="6" t="inlineStr"/>
-      <c r="J1532" s="6" t="inlineStr"/>
-    </row>
-    <row r="1533" ht="40" customHeight="1">
-      <c r="A1533" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B1533" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C1533" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1533" s="6" t="inlineStr"/>
-      <c r="E1533" s="6" t="inlineStr"/>
-      <c r="F1533" s="6" t="inlineStr"/>
-      <c r="G1533" s="6" t="inlineStr"/>
-      <c r="H1533" s="6" t="inlineStr"/>
-      <c r="I1533" s="6" t="inlineStr"/>
-      <c r="J1533" s="6" t="inlineStr"/>
-    </row>
-    <row r="1534" ht="40" customHeight="1">
-      <c r="A1534" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B1534" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C1534" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1534" s="6" t="inlineStr"/>
-      <c r="E1534" s="6" t="inlineStr"/>
-      <c r="F1534" s="6" t="inlineStr"/>
-      <c r="G1534" s="6" t="inlineStr"/>
-      <c r="H1534" s="6" t="inlineStr"/>
-      <c r="I1534" s="6" t="inlineStr"/>
-      <c r="J1534" s="6" t="inlineStr"/>
-    </row>
-    <row r="1535" ht="40" customHeight="1">
-      <c r="A1535" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B1535" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C1535" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1535" s="6" t="inlineStr"/>
-      <c r="E1535" s="6" t="inlineStr"/>
-      <c r="F1535" s="6" t="inlineStr"/>
-      <c r="G1535" s="6" t="inlineStr"/>
-      <c r="H1535" s="6" t="inlineStr"/>
-      <c r="I1535" s="6" t="inlineStr"/>
-      <c r="J1535" s="6" t="inlineStr"/>
-    </row>
-    <row r="1536" ht="40" customHeight="1">
-      <c r="A1536" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B1536" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C1536" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1536" s="6" t="inlineStr"/>
-      <c r="E1536" s="6" t="inlineStr"/>
-      <c r="F1536" s="6" t="inlineStr"/>
-      <c r="G1536" s="6" t="inlineStr"/>
-      <c r="H1536" s="6" t="inlineStr"/>
-      <c r="I1536" s="6" t="inlineStr"/>
-      <c r="J1536" s="6" t="inlineStr"/>
-    </row>
-    <row r="1537" ht="40" customHeight="1">
-      <c r="A1537" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B1537" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C1537" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1537" s="6" t="inlineStr"/>
-      <c r="E1537" s="6" t="inlineStr"/>
-      <c r="F1537" s="6" t="inlineStr"/>
-      <c r="G1537" s="6" t="inlineStr"/>
-      <c r="H1537" s="6" t="inlineStr"/>
-      <c r="I1537" s="6" t="inlineStr"/>
-      <c r="J1537" s="6" t="inlineStr"/>
-    </row>
-    <row r="1538" ht="40" customHeight="1">
-      <c r="A1538" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B1538" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C1538" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1538" s="6" t="inlineStr"/>
-      <c r="E1538" s="6" t="inlineStr"/>
-      <c r="F1538" s="6" t="inlineStr"/>
-      <c r="G1538" s="6" t="inlineStr"/>
-      <c r="H1538" s="6" t="inlineStr"/>
-      <c r="I1538" s="6" t="inlineStr"/>
-      <c r="J1538" s="6" t="inlineStr"/>
-    </row>
-    <row r="1539" ht="40" customHeight="1">
-      <c r="A1539" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B1539" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C1539" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1539" s="6" t="inlineStr"/>
-      <c r="E1539" s="6" t="inlineStr"/>
-      <c r="F1539" s="6" t="inlineStr"/>
-      <c r="G1539" s="6" t="inlineStr"/>
-      <c r="H1539" s="6" t="inlineStr"/>
-      <c r="I1539" s="6" t="inlineStr"/>
-      <c r="J1539" s="6" t="inlineStr"/>
-    </row>
-    <row r="1540" ht="40" customHeight="1">
-      <c r="A1540" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B1540" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C1540" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1540" s="6" t="inlineStr"/>
-      <c r="E1540" s="6" t="inlineStr"/>
-      <c r="F1540" s="6" t="inlineStr"/>
-      <c r="G1540" s="6" t="inlineStr"/>
-      <c r="H1540" s="6" t="inlineStr"/>
-      <c r="I1540" s="6" t="inlineStr"/>
-      <c r="J1540" s="6" t="inlineStr"/>
-    </row>
-    <row r="1541" ht="40" customHeight="1">
-      <c r="A1541" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B1541" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C1541" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D1541" s="6" t="inlineStr"/>
-      <c r="E1541" s="6" t="inlineStr"/>
-      <c r="F1541" s="6" t="inlineStr"/>
-      <c r="G1541" s="6" t="inlineStr"/>
-      <c r="H1541" s="6" t="inlineStr"/>
-      <c r="I1541" s="6" t="inlineStr"/>
-      <c r="J1541" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -54359,7 +52355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F771"/>
+  <dimension ref="A1:F741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -69398,7 +67394,7 @@
       </c>
       <c r="B612" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C612" s="13" t="inlineStr">
@@ -69422,7 +67418,7 @@
       </c>
       <c r="B613" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C613" s="13" t="inlineStr">
@@ -69446,7 +67442,7 @@
       </c>
       <c r="B614" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C614" s="13" t="inlineStr">
@@ -69470,7 +67466,7 @@
       </c>
       <c r="B615" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C615" s="13" t="inlineStr">
@@ -69494,7 +67490,7 @@
       </c>
       <c r="B616" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C616" s="13" t="inlineStr">
@@ -69518,7 +67514,7 @@
       </c>
       <c r="B617" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C617" s="13" t="inlineStr">
@@ -69542,7 +67538,7 @@
       </c>
       <c r="B618" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C618" s="13" t="inlineStr">
@@ -69566,7 +67562,7 @@
       </c>
       <c r="B619" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C619" s="13" t="inlineStr">
@@ -69590,7 +67586,7 @@
       </c>
       <c r="B620" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C620" s="13" t="inlineStr">
@@ -69614,7 +67610,7 @@
       </c>
       <c r="B621" s="8" t="inlineStr">
         <is>
-          <t>Crop Production and Management</t>
+          <t>Exploring the Investigative World of Science</t>
         </is>
       </c>
       <c r="C621" s="13" t="inlineStr">
@@ -69638,7 +67634,7 @@
       </c>
       <c r="B622" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C622" s="13" t="inlineStr">
@@ -69662,7 +67658,7 @@
       </c>
       <c r="B623" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C623" s="13" t="inlineStr">
@@ -69686,7 +67682,7 @@
       </c>
       <c r="B624" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C624" s="13" t="inlineStr">
@@ -69710,7 +67706,7 @@
       </c>
       <c r="B625" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C625" s="13" t="inlineStr">
@@ -69734,7 +67730,7 @@
       </c>
       <c r="B626" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C626" s="13" t="inlineStr">
@@ -69758,7 +67754,7 @@
       </c>
       <c r="B627" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C627" s="13" t="inlineStr">
@@ -69782,7 +67778,7 @@
       </c>
       <c r="B628" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C628" s="13" t="inlineStr">
@@ -69806,7 +67802,7 @@
       </c>
       <c r="B629" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C629" s="13" t="inlineStr">
@@ -69830,7 +67826,7 @@
       </c>
       <c r="B630" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C630" s="13" t="inlineStr">
@@ -69854,7 +67850,7 @@
       </c>
       <c r="B631" s="8" t="inlineStr">
         <is>
-          <t>Microorganisms: Friend and Foe</t>
+          <t>The Invisible Living World: Beyond Our Naked Eye</t>
         </is>
       </c>
       <c r="C631" s="13" t="inlineStr">
@@ -69878,7 +67874,7 @@
       </c>
       <c r="B632" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C632" s="13" t="inlineStr">
@@ -69902,7 +67898,7 @@
       </c>
       <c r="B633" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C633" s="13" t="inlineStr">
@@ -69926,7 +67922,7 @@
       </c>
       <c r="B634" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C634" s="13" t="inlineStr">
@@ -69950,7 +67946,7 @@
       </c>
       <c r="B635" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C635" s="13" t="inlineStr">
@@ -69974,7 +67970,7 @@
       </c>
       <c r="B636" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C636" s="13" t="inlineStr">
@@ -69998,7 +67994,7 @@
       </c>
       <c r="B637" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C637" s="13" t="inlineStr">
@@ -70022,7 +68018,7 @@
       </c>
       <c r="B638" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C638" s="13" t="inlineStr">
@@ -70046,7 +68042,7 @@
       </c>
       <c r="B639" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C639" s="13" t="inlineStr">
@@ -70070,7 +68066,7 @@
       </c>
       <c r="B640" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C640" s="13" t="inlineStr">
@@ -70094,7 +68090,7 @@
       </c>
       <c r="B641" s="8" t="inlineStr">
         <is>
-          <t>Synthetic Fibres and Plastics</t>
+          <t>Health: The Ultimate Treasure</t>
         </is>
       </c>
       <c r="C641" s="13" t="inlineStr">
@@ -70118,7 +68114,7 @@
       </c>
       <c r="B642" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C642" s="13" t="inlineStr">
@@ -70142,7 +68138,7 @@
       </c>
       <c r="B643" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C643" s="13" t="inlineStr">
@@ -70166,7 +68162,7 @@
       </c>
       <c r="B644" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C644" s="13" t="inlineStr">
@@ -70190,7 +68186,7 @@
       </c>
       <c r="B645" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C645" s="13" t="inlineStr">
@@ -70214,7 +68210,7 @@
       </c>
       <c r="B646" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C646" s="13" t="inlineStr">
@@ -70238,7 +68234,7 @@
       </c>
       <c r="B647" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C647" s="13" t="inlineStr">
@@ -70262,7 +68258,7 @@
       </c>
       <c r="B648" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C648" s="13" t="inlineStr">
@@ -70286,7 +68282,7 @@
       </c>
       <c r="B649" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C649" s="13" t="inlineStr">
@@ -70310,7 +68306,7 @@
       </c>
       <c r="B650" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C650" s="13" t="inlineStr">
@@ -70334,7 +68330,7 @@
       </c>
       <c r="B651" s="8" t="inlineStr">
         <is>
-          <t>Materials: Metals and Non-Metals</t>
+          <t>Electricity: Magnetic and Heating Effects</t>
         </is>
       </c>
       <c r="C651" s="13" t="inlineStr">
@@ -70358,7 +68354,7 @@
       </c>
       <c r="B652" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C652" s="13" t="inlineStr">
@@ -70382,7 +68378,7 @@
       </c>
       <c r="B653" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C653" s="13" t="inlineStr">
@@ -70406,7 +68402,7 @@
       </c>
       <c r="B654" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C654" s="13" t="inlineStr">
@@ -70430,7 +68426,7 @@
       </c>
       <c r="B655" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C655" s="13" t="inlineStr">
@@ -70454,7 +68450,7 @@
       </c>
       <c r="B656" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C656" s="13" t="inlineStr">
@@ -70478,7 +68474,7 @@
       </c>
       <c r="B657" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C657" s="13" t="inlineStr">
@@ -70502,7 +68498,7 @@
       </c>
       <c r="B658" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C658" s="13" t="inlineStr">
@@ -70526,7 +68522,7 @@
       </c>
       <c r="B659" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C659" s="13" t="inlineStr">
@@ -70550,7 +68546,7 @@
       </c>
       <c r="B660" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C660" s="13" t="inlineStr">
@@ -70574,7 +68570,7 @@
       </c>
       <c r="B661" s="8" t="inlineStr">
         <is>
-          <t>Coal and Petroleum</t>
+          <t>Exploring Forces</t>
         </is>
       </c>
       <c r="C661" s="13" t="inlineStr">
@@ -70598,7 +68594,7 @@
       </c>
       <c r="B662" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C662" s="13" t="inlineStr">
@@ -70622,7 +68618,7 @@
       </c>
       <c r="B663" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C663" s="13" t="inlineStr">
@@ -70646,7 +68642,7 @@
       </c>
       <c r="B664" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C664" s="13" t="inlineStr">
@@ -70670,7 +68666,7 @@
       </c>
       <c r="B665" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C665" s="13" t="inlineStr">
@@ -70694,7 +68690,7 @@
       </c>
       <c r="B666" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C666" s="13" t="inlineStr">
@@ -70718,7 +68714,7 @@
       </c>
       <c r="B667" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C667" s="13" t="inlineStr">
@@ -70742,7 +68738,7 @@
       </c>
       <c r="B668" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C668" s="13" t="inlineStr">
@@ -70766,7 +68762,7 @@
       </c>
       <c r="B669" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C669" s="13" t="inlineStr">
@@ -70790,7 +68786,7 @@
       </c>
       <c r="B670" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C670" s="13" t="inlineStr">
@@ -70814,7 +68810,7 @@
       </c>
       <c r="B671" s="8" t="inlineStr">
         <is>
-          <t>Combustion and Flame</t>
+          <t>Pressure, Winds, Storms, and Cyclones</t>
         </is>
       </c>
       <c r="C671" s="13" t="inlineStr">
@@ -70838,7 +68834,7 @@
       </c>
       <c r="B672" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C672" s="13" t="inlineStr">
@@ -70862,7 +68858,7 @@
       </c>
       <c r="B673" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C673" s="13" t="inlineStr">
@@ -70886,7 +68882,7 @@
       </c>
       <c r="B674" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C674" s="13" t="inlineStr">
@@ -70910,7 +68906,7 @@
       </c>
       <c r="B675" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C675" s="13" t="inlineStr">
@@ -70934,7 +68930,7 @@
       </c>
       <c r="B676" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C676" s="13" t="inlineStr">
@@ -70958,7 +68954,7 @@
       </c>
       <c r="B677" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C677" s="13" t="inlineStr">
@@ -70982,7 +68978,7 @@
       </c>
       <c r="B678" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C678" s="13" t="inlineStr">
@@ -71006,7 +69002,7 @@
       </c>
       <c r="B679" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C679" s="13" t="inlineStr">
@@ -71030,7 +69026,7 @@
       </c>
       <c r="B680" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C680" s="13" t="inlineStr">
@@ -71054,7 +69050,7 @@
       </c>
       <c r="B681" s="8" t="inlineStr">
         <is>
-          <t>Conservation of Plants and Animals</t>
+          <t>Particulate Nature of Matter</t>
         </is>
       </c>
       <c r="C681" s="13" t="inlineStr">
@@ -71078,7 +69074,7 @@
       </c>
       <c r="B682" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C682" s="13" t="inlineStr">
@@ -71102,7 +69098,7 @@
       </c>
       <c r="B683" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C683" s="13" t="inlineStr">
@@ -71126,7 +69122,7 @@
       </c>
       <c r="B684" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C684" s="13" t="inlineStr">
@@ -71150,7 +69146,7 @@
       </c>
       <c r="B685" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C685" s="13" t="inlineStr">
@@ -71174,7 +69170,7 @@
       </c>
       <c r="B686" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C686" s="13" t="inlineStr">
@@ -71198,7 +69194,7 @@
       </c>
       <c r="B687" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C687" s="13" t="inlineStr">
@@ -71222,7 +69218,7 @@
       </c>
       <c r="B688" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C688" s="13" t="inlineStr">
@@ -71246,7 +69242,7 @@
       </c>
       <c r="B689" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C689" s="13" t="inlineStr">
@@ -71270,7 +69266,7 @@
       </c>
       <c r="B690" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C690" s="13" t="inlineStr">
@@ -71294,7 +69290,7 @@
       </c>
       <c r="B691" s="8" t="inlineStr">
         <is>
-          <t>Cell — Structure and Functions</t>
+          <t>Nature of Matter: Elements, Compounds, and Mixtures</t>
         </is>
       </c>
       <c r="C691" s="13" t="inlineStr">
@@ -71318,7 +69314,7 @@
       </c>
       <c r="B692" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C692" s="13" t="inlineStr">
@@ -71342,7 +69338,7 @@
       </c>
       <c r="B693" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C693" s="13" t="inlineStr">
@@ -71366,7 +69362,7 @@
       </c>
       <c r="B694" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C694" s="13" t="inlineStr">
@@ -71390,7 +69386,7 @@
       </c>
       <c r="B695" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C695" s="13" t="inlineStr">
@@ -71414,7 +69410,7 @@
       </c>
       <c r="B696" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C696" s="13" t="inlineStr">
@@ -71438,7 +69434,7 @@
       </c>
       <c r="B697" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C697" s="13" t="inlineStr">
@@ -71462,7 +69458,7 @@
       </c>
       <c r="B698" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C698" s="13" t="inlineStr">
@@ -71486,7 +69482,7 @@
       </c>
       <c r="B699" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C699" s="13" t="inlineStr">
@@ -71510,7 +69506,7 @@
       </c>
       <c r="B700" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C700" s="13" t="inlineStr">
@@ -71534,7 +69530,7 @@
       </c>
       <c r="B701" s="8" t="inlineStr">
         <is>
-          <t>Reproduction in Animals</t>
+          <t>The Amazing World of Solutes, Solvents, and Solutions</t>
         </is>
       </c>
       <c r="C701" s="13" t="inlineStr">
@@ -71558,7 +69554,7 @@
       </c>
       <c r="B702" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C702" s="13" t="inlineStr">
@@ -71582,7 +69578,7 @@
       </c>
       <c r="B703" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C703" s="13" t="inlineStr">
@@ -71606,7 +69602,7 @@
       </c>
       <c r="B704" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C704" s="13" t="inlineStr">
@@ -71630,7 +69626,7 @@
       </c>
       <c r="B705" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C705" s="13" t="inlineStr">
@@ -71654,7 +69650,7 @@
       </c>
       <c r="B706" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C706" s="13" t="inlineStr">
@@ -71678,7 +69674,7 @@
       </c>
       <c r="B707" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C707" s="13" t="inlineStr">
@@ -71702,7 +69698,7 @@
       </c>
       <c r="B708" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C708" s="13" t="inlineStr">
@@ -71726,7 +69722,7 @@
       </c>
       <c r="B709" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C709" s="13" t="inlineStr">
@@ -71750,7 +69746,7 @@
       </c>
       <c r="B710" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C710" s="13" t="inlineStr">
@@ -71774,7 +69770,7 @@
       </c>
       <c r="B711" s="8" t="inlineStr">
         <is>
-          <t>Reaching the Age of Adolescence</t>
+          <t>Light: Mirrors and Lenses</t>
         </is>
       </c>
       <c r="C711" s="13" t="inlineStr">
@@ -71798,7 +69794,7 @@
       </c>
       <c r="B712" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C712" s="13" t="inlineStr">
@@ -71822,7 +69818,7 @@
       </c>
       <c r="B713" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C713" s="13" t="inlineStr">
@@ -71846,7 +69842,7 @@
       </c>
       <c r="B714" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C714" s="13" t="inlineStr">
@@ -71870,7 +69866,7 @@
       </c>
       <c r="B715" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C715" s="13" t="inlineStr">
@@ -71894,7 +69890,7 @@
       </c>
       <c r="B716" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C716" s="13" t="inlineStr">
@@ -71918,7 +69914,7 @@
       </c>
       <c r="B717" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C717" s="13" t="inlineStr">
@@ -71942,7 +69938,7 @@
       </c>
       <c r="B718" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C718" s="13" t="inlineStr">
@@ -71966,7 +69962,7 @@
       </c>
       <c r="B719" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C719" s="13" t="inlineStr">
@@ -71990,7 +69986,7 @@
       </c>
       <c r="B720" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C720" s="13" t="inlineStr">
@@ -72014,7 +70010,7 @@
       </c>
       <c r="B721" s="8" t="inlineStr">
         <is>
-          <t>Force and Pressure</t>
+          <t>Keeping Time with the Skies</t>
         </is>
       </c>
       <c r="C721" s="13" t="inlineStr">
@@ -72038,7 +70034,7 @@
       </c>
       <c r="B722" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C722" s="13" t="inlineStr">
@@ -72062,7 +70058,7 @@
       </c>
       <c r="B723" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C723" s="13" t="inlineStr">
@@ -72086,7 +70082,7 @@
       </c>
       <c r="B724" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C724" s="13" t="inlineStr">
@@ -72110,7 +70106,7 @@
       </c>
       <c r="B725" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C725" s="13" t="inlineStr">
@@ -72134,7 +70130,7 @@
       </c>
       <c r="B726" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C726" s="13" t="inlineStr">
@@ -72158,7 +70154,7 @@
       </c>
       <c r="B727" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C727" s="13" t="inlineStr">
@@ -72182,7 +70178,7 @@
       </c>
       <c r="B728" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C728" s="13" t="inlineStr">
@@ -72206,7 +70202,7 @@
       </c>
       <c r="B729" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C729" s="13" t="inlineStr">
@@ -72230,7 +70226,7 @@
       </c>
       <c r="B730" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C730" s="13" t="inlineStr">
@@ -72254,7 +70250,7 @@
       </c>
       <c r="B731" s="8" t="inlineStr">
         <is>
-          <t>Friction</t>
+          <t>How Nature Works in Harmony</t>
         </is>
       </c>
       <c r="C731" s="13" t="inlineStr">
@@ -72278,7 +70274,7 @@
       </c>
       <c r="B732" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C732" s="13" t="inlineStr">
@@ -72302,7 +70298,7 @@
       </c>
       <c r="B733" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C733" s="13" t="inlineStr">
@@ -72326,7 +70322,7 @@
       </c>
       <c r="B734" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C734" s="13" t="inlineStr">
@@ -72350,7 +70346,7 @@
       </c>
       <c r="B735" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C735" s="13" t="inlineStr">
@@ -72374,7 +70370,7 @@
       </c>
       <c r="B736" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C736" s="13" t="inlineStr">
@@ -72398,7 +70394,7 @@
       </c>
       <c r="B737" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C737" s="13" t="inlineStr">
@@ -72422,7 +70418,7 @@
       </c>
       <c r="B738" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C738" s="13" t="inlineStr">
@@ -72446,7 +70442,7 @@
       </c>
       <c r="B739" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C739" s="13" t="inlineStr">
@@ -72470,7 +70466,7 @@
       </c>
       <c r="B740" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C740" s="13" t="inlineStr">
@@ -72494,7 +70490,7 @@
       </c>
       <c r="B741" s="8" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Our Home: Earth, a Unique Life Sustaining Planet</t>
         </is>
       </c>
       <c r="C741" s="13" t="inlineStr">
@@ -72505,726 +70501,6 @@
       <c r="D741" s="6" t="inlineStr"/>
       <c r="E741" s="6" t="inlineStr"/>
       <c r="F741" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="742" ht="50" customHeight="1">
-      <c r="A742" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B742" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C742" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D742" s="6" t="inlineStr"/>
-      <c r="E742" s="6" t="inlineStr"/>
-      <c r="F742" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="743" ht="50" customHeight="1">
-      <c r="A743" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B743" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C743" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D743" s="6" t="inlineStr"/>
-      <c r="E743" s="6" t="inlineStr"/>
-      <c r="F743" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="744" ht="50" customHeight="1">
-      <c r="A744" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B744" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C744" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D744" s="6" t="inlineStr"/>
-      <c r="E744" s="6" t="inlineStr"/>
-      <c r="F744" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="745" ht="50" customHeight="1">
-      <c r="A745" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B745" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C745" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D745" s="6" t="inlineStr"/>
-      <c r="E745" s="6" t="inlineStr"/>
-      <c r="F745" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="746" ht="50" customHeight="1">
-      <c r="A746" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B746" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C746" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D746" s="6" t="inlineStr"/>
-      <c r="E746" s="6" t="inlineStr"/>
-      <c r="F746" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="747" ht="50" customHeight="1">
-      <c r="A747" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B747" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C747" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D747" s="6" t="inlineStr"/>
-      <c r="E747" s="6" t="inlineStr"/>
-      <c r="F747" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="748" ht="50" customHeight="1">
-      <c r="A748" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B748" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C748" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D748" s="6" t="inlineStr"/>
-      <c r="E748" s="6" t="inlineStr"/>
-      <c r="F748" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="749" ht="50" customHeight="1">
-      <c r="A749" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B749" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C749" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D749" s="6" t="inlineStr"/>
-      <c r="E749" s="6" t="inlineStr"/>
-      <c r="F749" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="750" ht="50" customHeight="1">
-      <c r="A750" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B750" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C750" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D750" s="6" t="inlineStr"/>
-      <c r="E750" s="6" t="inlineStr"/>
-      <c r="F750" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="751" ht="50" customHeight="1">
-      <c r="A751" s="7" t="inlineStr">
-        <is>
-          <t>8-science-14</t>
-        </is>
-      </c>
-      <c r="B751" s="8" t="inlineStr">
-        <is>
-          <t>Chemical Effects of Electric Current</t>
-        </is>
-      </c>
-      <c r="C751" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D751" s="6" t="inlineStr"/>
-      <c r="E751" s="6" t="inlineStr"/>
-      <c r="F751" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="752" ht="50" customHeight="1">
-      <c r="A752" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B752" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C752" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D752" s="6" t="inlineStr"/>
-      <c r="E752" s="6" t="inlineStr"/>
-      <c r="F752" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="753" ht="50" customHeight="1">
-      <c r="A753" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B753" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C753" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D753" s="6" t="inlineStr"/>
-      <c r="E753" s="6" t="inlineStr"/>
-      <c r="F753" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="754" ht="50" customHeight="1">
-      <c r="A754" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B754" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C754" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D754" s="6" t="inlineStr"/>
-      <c r="E754" s="6" t="inlineStr"/>
-      <c r="F754" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="755" ht="50" customHeight="1">
-      <c r="A755" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B755" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C755" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D755" s="6" t="inlineStr"/>
-      <c r="E755" s="6" t="inlineStr"/>
-      <c r="F755" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="756" ht="50" customHeight="1">
-      <c r="A756" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B756" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C756" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D756" s="6" t="inlineStr"/>
-      <c r="E756" s="6" t="inlineStr"/>
-      <c r="F756" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="757" ht="50" customHeight="1">
-      <c r="A757" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B757" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C757" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D757" s="6" t="inlineStr"/>
-      <c r="E757" s="6" t="inlineStr"/>
-      <c r="F757" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="758" ht="50" customHeight="1">
-      <c r="A758" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B758" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C758" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D758" s="6" t="inlineStr"/>
-      <c r="E758" s="6" t="inlineStr"/>
-      <c r="F758" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="759" ht="50" customHeight="1">
-      <c r="A759" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B759" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C759" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D759" s="6" t="inlineStr"/>
-      <c r="E759" s="6" t="inlineStr"/>
-      <c r="F759" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="760" ht="50" customHeight="1">
-      <c r="A760" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B760" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C760" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D760" s="6" t="inlineStr"/>
-      <c r="E760" s="6" t="inlineStr"/>
-      <c r="F760" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="761" ht="50" customHeight="1">
-      <c r="A761" s="7" t="inlineStr">
-        <is>
-          <t>8-science-15</t>
-        </is>
-      </c>
-      <c r="B761" s="8" t="inlineStr">
-        <is>
-          <t>Some Natural Phenomena</t>
-        </is>
-      </c>
-      <c r="C761" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D761" s="6" t="inlineStr"/>
-      <c r="E761" s="6" t="inlineStr"/>
-      <c r="F761" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="762" ht="50" customHeight="1">
-      <c r="A762" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B762" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C762" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D762" s="6" t="inlineStr"/>
-      <c r="E762" s="6" t="inlineStr"/>
-      <c r="F762" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="763" ht="50" customHeight="1">
-      <c r="A763" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B763" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C763" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D763" s="6" t="inlineStr"/>
-      <c r="E763" s="6" t="inlineStr"/>
-      <c r="F763" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="764" ht="50" customHeight="1">
-      <c r="A764" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B764" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C764" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D764" s="6" t="inlineStr"/>
-      <c r="E764" s="6" t="inlineStr"/>
-      <c r="F764" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="765" ht="50" customHeight="1">
-      <c r="A765" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B765" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C765" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D765" s="6" t="inlineStr"/>
-      <c r="E765" s="6" t="inlineStr"/>
-      <c r="F765" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="766" ht="50" customHeight="1">
-      <c r="A766" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B766" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C766" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D766" s="6" t="inlineStr"/>
-      <c r="E766" s="6" t="inlineStr"/>
-      <c r="F766" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="767" ht="50" customHeight="1">
-      <c r="A767" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B767" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C767" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D767" s="6" t="inlineStr"/>
-      <c r="E767" s="6" t="inlineStr"/>
-      <c r="F767" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="768" ht="50" customHeight="1">
-      <c r="A768" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B768" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C768" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D768" s="6" t="inlineStr"/>
-      <c r="E768" s="6" t="inlineStr"/>
-      <c r="F768" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="769" ht="50" customHeight="1">
-      <c r="A769" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B769" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C769" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D769" s="6" t="inlineStr"/>
-      <c r="E769" s="6" t="inlineStr"/>
-      <c r="F769" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="770" ht="50" customHeight="1">
-      <c r="A770" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B770" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C770" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D770" s="6" t="inlineStr"/>
-      <c r="E770" s="6" t="inlineStr"/>
-      <c r="F770" s="16" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-    </row>
-    <row r="771" ht="50" customHeight="1">
-      <c r="A771" s="7" t="inlineStr">
-        <is>
-          <t>8-science-16</t>
-        </is>
-      </c>
-      <c r="B771" s="8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C771" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D771" s="6" t="inlineStr"/>
-      <c r="E771" s="6" t="inlineStr"/>
-      <c r="F771" s="16" t="inlineStr">
         <is>
           <t>short</t>
         </is>
